--- a/Resultados.xlsx
+++ b/Resultados.xlsx
@@ -436,102 +436,102 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Atlético Nacional</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Deportivo Pasto</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Deportes Tolima</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Once Caldas</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Junior</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>América de Cali</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Deportivo Cali</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Internacional de Bogotá</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Millonarios</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Llaneros</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>Atlético Bucaramanga</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Atlético Nacional</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Junior</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Santa Fe</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Águilas Doradas</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Independiente Medellín</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Fortaleza CEIF</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Deportes Tolima</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Llaneros</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Águilas Doradas</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>América de Cali</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Alianza F. C.</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Santa Fe</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Once Caldas</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Millonarios</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>Deportivo Cali</t>
-        </is>
-      </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>Unión Magdalena</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
+          <t>Cúcuta Deportivo</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Jaguares</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Alianza Valledupar</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Boyacá Chicó</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
           <t>Deportivo Pereira</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>Deportivo Pasto</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Envigado F. C.</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>Boyacá Chicó</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>La Equidad</t>
         </is>
       </c>
     </row>
@@ -540,34 +540,34 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>40.38</v>
+        <v>23.546</v>
       </c>
       <c r="C2" t="n">
-        <v>27.949</v>
+        <v>31.399</v>
       </c>
       <c r="D2" t="n">
-        <v>17.155</v>
+        <v>20.315</v>
       </c>
       <c r="E2" t="n">
-        <v>10.141</v>
+        <v>11.413</v>
       </c>
       <c r="F2" t="n">
-        <v>3.48</v>
+        <v>5.964</v>
       </c>
       <c r="G2" t="n">
-        <v>0.697</v>
+        <v>4.94</v>
       </c>
       <c r="H2" t="n">
-        <v>0.183</v>
+        <v>2.211</v>
       </c>
       <c r="I2" t="n">
-        <v>0.015</v>
+        <v>0.168</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>0.004</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -605,37 +605,37 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>26.233</v>
+        <v>20.054</v>
       </c>
       <c r="C3" t="n">
-        <v>23.848</v>
+        <v>19.559</v>
       </c>
       <c r="D3" t="n">
-        <v>20.581</v>
+        <v>17.539</v>
       </c>
       <c r="E3" t="n">
-        <v>13.822</v>
+        <v>13.961</v>
       </c>
       <c r="F3" t="n">
-        <v>9.619</v>
+        <v>9.045</v>
       </c>
       <c r="G3" t="n">
-        <v>3.919</v>
+        <v>11.55</v>
       </c>
       <c r="H3" t="n">
-        <v>1.614</v>
+        <v>6.925000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>0.349</v>
+        <v>0.9900000000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>0.015</v>
+        <v>0.303</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>0.073</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -670,40 +670,40 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>14.475</v>
+        <v>14.735</v>
       </c>
       <c r="C4" t="n">
-        <v>18.123</v>
+        <v>14.765</v>
       </c>
       <c r="D4" t="n">
-        <v>17.9</v>
+        <v>15.069</v>
       </c>
       <c r="E4" t="n">
-        <v>16.834</v>
+        <v>14.132</v>
       </c>
       <c r="F4" t="n">
-        <v>14.071</v>
+        <v>11.398</v>
       </c>
       <c r="G4" t="n">
-        <v>10.355</v>
+        <v>14.72</v>
       </c>
       <c r="H4" t="n">
-        <v>5.689</v>
+        <v>10.544</v>
       </c>
       <c r="I4" t="n">
-        <v>2.189</v>
+        <v>2.786</v>
       </c>
       <c r="J4" t="n">
-        <v>0.357</v>
+        <v>1.241</v>
       </c>
       <c r="K4" t="n">
-        <v>0.006</v>
+        <v>0.604</v>
       </c>
       <c r="L4" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="M4" t="n">
         <v>0.001</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -735,43 +735,43 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>9.897</v>
+        <v>12.102</v>
       </c>
       <c r="C5" t="n">
-        <v>11.708</v>
+        <v>11.531</v>
       </c>
       <c r="D5" t="n">
-        <v>14.669</v>
+        <v>12.728</v>
       </c>
       <c r="E5" t="n">
-        <v>17.851</v>
+        <v>13.513</v>
       </c>
       <c r="F5" t="n">
-        <v>15.238</v>
+        <v>12.811</v>
       </c>
       <c r="G5" t="n">
-        <v>13.448</v>
+        <v>15.269</v>
       </c>
       <c r="H5" t="n">
-        <v>9.167</v>
+        <v>12.097</v>
       </c>
       <c r="I5" t="n">
-        <v>5.657999999999999</v>
+        <v>4.87</v>
       </c>
       <c r="J5" t="n">
-        <v>2.09</v>
+        <v>2.752</v>
       </c>
       <c r="K5" t="n">
-        <v>0.248</v>
+        <v>2.255</v>
       </c>
       <c r="L5" t="n">
-        <v>0.026</v>
+        <v>0.044</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>0.027</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -800,43 +800,43 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>5.263</v>
+        <v>9.988</v>
       </c>
       <c r="C6" t="n">
-        <v>8.445</v>
+        <v>8.529</v>
       </c>
       <c r="D6" t="n">
-        <v>11.942</v>
+        <v>10.772</v>
       </c>
       <c r="E6" t="n">
-        <v>14.579</v>
+        <v>12.57</v>
       </c>
       <c r="F6" t="n">
-        <v>16.265</v>
+        <v>13.281</v>
       </c>
       <c r="G6" t="n">
-        <v>15.233</v>
+        <v>14.404</v>
       </c>
       <c r="H6" t="n">
-        <v>12.263</v>
+        <v>13.519</v>
       </c>
       <c r="I6" t="n">
-        <v>9.042</v>
+        <v>6.869</v>
       </c>
       <c r="J6" t="n">
-        <v>5.151</v>
+        <v>4.414</v>
       </c>
       <c r="K6" t="n">
-        <v>1.504</v>
+        <v>5.256</v>
       </c>
       <c r="L6" t="n">
-        <v>0.295</v>
+        <v>0.227</v>
       </c>
       <c r="M6" t="n">
-        <v>0.018</v>
+        <v>0.166</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -865,46 +865,46 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>2.443</v>
+        <v>7.613</v>
       </c>
       <c r="C7" t="n">
-        <v>5.316</v>
+        <v>6.254999999999999</v>
       </c>
       <c r="D7" t="n">
-        <v>9.637</v>
+        <v>8.888</v>
       </c>
       <c r="E7" t="n">
-        <v>10.855</v>
+        <v>11.23</v>
       </c>
       <c r="F7" t="n">
-        <v>14.773</v>
+        <v>12.86</v>
       </c>
       <c r="G7" t="n">
-        <v>15.133</v>
+        <v>12.411</v>
       </c>
       <c r="H7" t="n">
-        <v>14.664</v>
+        <v>14.314</v>
       </c>
       <c r="I7" t="n">
-        <v>11.687</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="J7" t="n">
-        <v>8.552</v>
+        <v>6.638</v>
       </c>
       <c r="K7" t="n">
-        <v>4.873</v>
+        <v>8.473000000000001</v>
       </c>
       <c r="L7" t="n">
-        <v>1.804</v>
+        <v>0.8630000000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>0.242</v>
+        <v>0.843</v>
       </c>
       <c r="N7" t="n">
-        <v>0.021</v>
+        <v>0.062</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
@@ -930,52 +930,52 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>1.092</v>
+        <v>5.518</v>
       </c>
       <c r="C8" t="n">
-        <v>2.666</v>
+        <v>4.170999999999999</v>
       </c>
       <c r="D8" t="n">
-        <v>4.572</v>
+        <v>6.406000000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>7.535</v>
+        <v>9.131</v>
       </c>
       <c r="F8" t="n">
-        <v>11.206</v>
+        <v>11.622</v>
       </c>
       <c r="G8" t="n">
-        <v>13.112</v>
+        <v>10.256</v>
       </c>
       <c r="H8" t="n">
-        <v>15.784</v>
+        <v>13.519</v>
       </c>
       <c r="I8" t="n">
-        <v>14.832</v>
+        <v>12.55</v>
       </c>
       <c r="J8" t="n">
-        <v>11.946</v>
+        <v>9.754999999999999</v>
       </c>
       <c r="K8" t="n">
-        <v>9.648</v>
+        <v>12.043</v>
       </c>
       <c r="L8" t="n">
-        <v>5.542</v>
+        <v>2.074</v>
       </c>
       <c r="M8" t="n">
-        <v>1.709</v>
+        <v>2.57</v>
       </c>
       <c r="N8" t="n">
-        <v>0.288</v>
+        <v>0.269</v>
       </c>
       <c r="O8" t="n">
-        <v>0.068</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>0.026</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>0.003</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -995,52 +995,52 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>0.204</v>
+        <v>3.307</v>
       </c>
       <c r="C9" t="n">
-        <v>1.408</v>
+        <v>2.292</v>
       </c>
       <c r="D9" t="n">
-        <v>2.066</v>
+        <v>4.355</v>
       </c>
       <c r="E9" t="n">
-        <v>4.376</v>
+        <v>6.35</v>
       </c>
       <c r="F9" t="n">
-        <v>7.611</v>
+        <v>9.157999999999999</v>
       </c>
       <c r="G9" t="n">
-        <v>10.667</v>
+        <v>7.819</v>
       </c>
       <c r="H9" t="n">
-        <v>13.309</v>
+        <v>11.342</v>
       </c>
       <c r="I9" t="n">
-        <v>15.23</v>
+        <v>14.28</v>
       </c>
       <c r="J9" t="n">
-        <v>14.969</v>
+        <v>13.078</v>
       </c>
       <c r="K9" t="n">
-        <v>12.81</v>
+        <v>16.211</v>
       </c>
       <c r="L9" t="n">
-        <v>9.56</v>
+        <v>4.119</v>
       </c>
       <c r="M9" t="n">
-        <v>5.202</v>
+        <v>5.508</v>
       </c>
       <c r="N9" t="n">
-        <v>1.84</v>
+        <v>1.064</v>
       </c>
       <c r="O9" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.662</v>
       </c>
       <c r="P9" t="n">
-        <v>0.062</v>
+        <v>0.379</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.001</v>
+        <v>0.076</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -1060,58 +1060,58 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>0.012</v>
+        <v>1.806</v>
       </c>
       <c r="C10" t="n">
-        <v>0.471</v>
+        <v>0.9740000000000001</v>
       </c>
       <c r="D10" t="n">
-        <v>1.116</v>
+        <v>2.439</v>
       </c>
       <c r="E10" t="n">
-        <v>2.422</v>
+        <v>4.299</v>
       </c>
       <c r="F10" t="n">
-        <v>4.226</v>
+        <v>6.587999999999999</v>
       </c>
       <c r="G10" t="n">
-        <v>8.407999999999999</v>
+        <v>4.962</v>
       </c>
       <c r="H10" t="n">
-        <v>11.073</v>
+        <v>8.227</v>
       </c>
       <c r="I10" t="n">
-        <v>13.31</v>
+        <v>14.531</v>
       </c>
       <c r="J10" t="n">
-        <v>15.943</v>
+        <v>15.043</v>
       </c>
       <c r="K10" t="n">
-        <v>14.274</v>
+        <v>17.932</v>
       </c>
       <c r="L10" t="n">
-        <v>11.603</v>
+        <v>6.875000000000001</v>
       </c>
       <c r="M10" t="n">
-        <v>8.970000000000001</v>
+        <v>8.225</v>
       </c>
       <c r="N10" t="n">
-        <v>4.852</v>
+        <v>2.679</v>
       </c>
       <c r="O10" t="n">
-        <v>2.779</v>
+        <v>2.516</v>
       </c>
       <c r="P10" t="n">
-        <v>0.51</v>
+        <v>2.311</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.031</v>
+        <v>0.5720000000000001</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="T10" t="n">
         <v>0</v>
@@ -1125,61 +1125,61 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>0.001</v>
+        <v>0.876</v>
       </c>
       <c r="C11" t="n">
-        <v>0.066</v>
+        <v>0.4349999999999999</v>
       </c>
       <c r="D11" t="n">
-        <v>0.339</v>
+        <v>1.099</v>
       </c>
       <c r="E11" t="n">
-        <v>1.27</v>
+        <v>2.234</v>
       </c>
       <c r="F11" t="n">
-        <v>2.286</v>
+        <v>4.36</v>
       </c>
       <c r="G11" t="n">
-        <v>5.258</v>
+        <v>2.645</v>
       </c>
       <c r="H11" t="n">
-        <v>8.383000000000001</v>
+        <v>4.523</v>
       </c>
       <c r="I11" t="n">
-        <v>11.42</v>
+        <v>12.996</v>
       </c>
       <c r="J11" t="n">
-        <v>13.75</v>
+        <v>15.012</v>
       </c>
       <c r="K11" t="n">
-        <v>14.668</v>
+        <v>14.492</v>
       </c>
       <c r="L11" t="n">
-        <v>13.651</v>
+        <v>9.944000000000001</v>
       </c>
       <c r="M11" t="n">
-        <v>11.911</v>
+        <v>11.315</v>
       </c>
       <c r="N11" t="n">
-        <v>8.552999999999999</v>
+        <v>4.99</v>
       </c>
       <c r="O11" t="n">
-        <v>6.045</v>
+        <v>5.521</v>
       </c>
       <c r="P11" t="n">
-        <v>1.797</v>
+        <v>6.630999999999999</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.5660000000000001</v>
+        <v>2.704</v>
       </c>
       <c r="R11" t="n">
-        <v>0.035</v>
+        <v>0.209</v>
       </c>
       <c r="S11" t="n">
-        <v>0.001</v>
+        <v>0.012</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
@@ -1190,61 +1190,61 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>0.289</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>0.08800000000000001</v>
       </c>
       <c r="D12" t="n">
-        <v>0.023</v>
+        <v>0.321</v>
       </c>
       <c r="E12" t="n">
-        <v>0.292</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>1.025</v>
+        <v>1.793</v>
       </c>
       <c r="G12" t="n">
-        <v>2.423</v>
+        <v>0.876</v>
       </c>
       <c r="H12" t="n">
-        <v>4.446</v>
+        <v>1.962</v>
       </c>
       <c r="I12" t="n">
-        <v>8.583</v>
+        <v>8.685</v>
       </c>
       <c r="J12" t="n">
-        <v>10.992</v>
+        <v>11.827</v>
       </c>
       <c r="K12" t="n">
-        <v>13.556</v>
+        <v>10.603</v>
       </c>
       <c r="L12" t="n">
-        <v>15.036</v>
+        <v>12.272</v>
       </c>
       <c r="M12" t="n">
-        <v>14.827</v>
+        <v>13.316</v>
       </c>
       <c r="N12" t="n">
-        <v>11.795</v>
+        <v>7.847</v>
       </c>
       <c r="O12" t="n">
-        <v>8.244</v>
+        <v>9.025</v>
       </c>
       <c r="P12" t="n">
-        <v>4.366</v>
+        <v>11.842</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.501</v>
+        <v>6.957000000000001</v>
       </c>
       <c r="R12" t="n">
-        <v>0.877</v>
+        <v>1.305</v>
       </c>
       <c r="S12" t="n">
-        <v>0.014</v>
+        <v>0.133</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>0.039</v>
       </c>
       <c r="U12" t="n">
         <v>0</v>
@@ -1255,64 +1255,64 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.137</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>0.067</v>
       </c>
       <c r="E13" t="n">
-        <v>0.023</v>
+        <v>0.293</v>
       </c>
       <c r="F13" t="n">
-        <v>0.192</v>
+        <v>0.707</v>
       </c>
       <c r="G13" t="n">
-        <v>1.148</v>
+        <v>0.141</v>
       </c>
       <c r="H13" t="n">
-        <v>2.238</v>
+        <v>0.718</v>
       </c>
       <c r="I13" t="n">
-        <v>4.354</v>
+        <v>5.737</v>
       </c>
       <c r="J13" t="n">
-        <v>7.883</v>
+        <v>8.433999999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>10.986</v>
+        <v>6.383</v>
       </c>
       <c r="L13" t="n">
-        <v>13.273</v>
+        <v>12.679</v>
       </c>
       <c r="M13" t="n">
-        <v>14.434</v>
+        <v>14.243</v>
       </c>
       <c r="N13" t="n">
-        <v>13.746</v>
+        <v>9.635999999999999</v>
       </c>
       <c r="O13" t="n">
-        <v>10.087</v>
+        <v>11.737</v>
       </c>
       <c r="P13" t="n">
-        <v>7.242</v>
+        <v>13.709</v>
       </c>
       <c r="Q13" t="n">
-        <v>9.829000000000001</v>
+        <v>11.083</v>
       </c>
       <c r="R13" t="n">
-        <v>4.354</v>
+        <v>3.468</v>
       </c>
       <c r="S13" t="n">
-        <v>0.202</v>
+        <v>0.5369999999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>0.009000000000000001</v>
+        <v>0.283</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>0.006</v>
       </c>
     </row>
     <row r="14">
@@ -1320,64 +1320,64 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.028</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>0.052</v>
       </c>
       <c r="F14" t="n">
-        <v>0.008</v>
+        <v>0.338</v>
       </c>
       <c r="G14" t="n">
-        <v>0.189</v>
+        <v>0.006999999999999999</v>
       </c>
       <c r="H14" t="n">
-        <v>0.951</v>
+        <v>0.094</v>
       </c>
       <c r="I14" t="n">
-        <v>1.891</v>
+        <v>3.469</v>
       </c>
       <c r="J14" t="n">
-        <v>4.112</v>
+        <v>5.423</v>
       </c>
       <c r="K14" t="n">
-        <v>7.471</v>
+        <v>3.108</v>
       </c>
       <c r="L14" t="n">
-        <v>10.096</v>
+        <v>12.492</v>
       </c>
       <c r="M14" t="n">
-        <v>11.377</v>
+        <v>12.87</v>
       </c>
       <c r="N14" t="n">
-        <v>14.216</v>
+        <v>11.196</v>
       </c>
       <c r="O14" t="n">
-        <v>11.853</v>
+        <v>13.556</v>
       </c>
       <c r="P14" t="n">
-        <v>9.991</v>
+        <v>15.572</v>
       </c>
       <c r="Q14" t="n">
-        <v>15.546</v>
+        <v>13.523</v>
       </c>
       <c r="R14" t="n">
-        <v>10.378</v>
+        <v>5.827</v>
       </c>
       <c r="S14" t="n">
-        <v>1.579</v>
+        <v>1.336</v>
       </c>
       <c r="T14" t="n">
-        <v>0.333</v>
+        <v>1.048</v>
       </c>
       <c r="U14" t="n">
-        <v>0.009000000000000001</v>
+        <v>0.059</v>
       </c>
     </row>
     <row r="15">
@@ -1385,7 +1385,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
@@ -1394,55 +1394,55 @@
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>0.06899999999999999</v>
       </c>
       <c r="G15" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>0.218</v>
+        <v>0.005</v>
       </c>
       <c r="I15" t="n">
-        <v>1.023</v>
+        <v>1.546</v>
       </c>
       <c r="J15" t="n">
-        <v>2.001</v>
+        <v>3.404</v>
       </c>
       <c r="K15" t="n">
-        <v>4.821000000000001</v>
+        <v>1.728</v>
       </c>
       <c r="L15" t="n">
-        <v>8.1</v>
+        <v>11.077</v>
       </c>
       <c r="M15" t="n">
-        <v>9.529</v>
+        <v>11.072</v>
       </c>
       <c r="N15" t="n">
-        <v>12.579</v>
+        <v>12.136</v>
       </c>
       <c r="O15" t="n">
-        <v>13.562</v>
+        <v>13.705</v>
       </c>
       <c r="P15" t="n">
-        <v>12.916</v>
+        <v>14.398</v>
       </c>
       <c r="Q15" t="n">
-        <v>15.812</v>
+        <v>15.954</v>
       </c>
       <c r="R15" t="n">
-        <v>13.624</v>
+        <v>8.692</v>
       </c>
       <c r="S15" t="n">
-        <v>4.148000000000001</v>
+        <v>2.847</v>
       </c>
       <c r="T15" t="n">
-        <v>1.405</v>
+        <v>2.998</v>
       </c>
       <c r="U15" t="n">
-        <v>0.252</v>
+        <v>0.366</v>
       </c>
     </row>
     <row r="16">
@@ -1462,52 +1462,52 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>0.006</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>0.018</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>0.37</v>
+        <v>0.628</v>
       </c>
       <c r="J16" t="n">
-        <v>1.435</v>
+        <v>1.609</v>
       </c>
       <c r="K16" t="n">
-        <v>2.709</v>
+        <v>0.695</v>
       </c>
       <c r="L16" t="n">
-        <v>5.502</v>
+        <v>9.544</v>
       </c>
       <c r="M16" t="n">
-        <v>8.268000000000001</v>
+        <v>8.827</v>
       </c>
       <c r="N16" t="n">
-        <v>10.289</v>
+        <v>13.017</v>
       </c>
       <c r="O16" t="n">
-        <v>13.211</v>
+        <v>13.479</v>
       </c>
       <c r="P16" t="n">
-        <v>14.957</v>
+        <v>12.615</v>
       </c>
       <c r="Q16" t="n">
-        <v>17.034</v>
+        <v>15.99</v>
       </c>
       <c r="R16" t="n">
-        <v>14.809</v>
+        <v>11.809</v>
       </c>
       <c r="S16" t="n">
-        <v>6.764</v>
+        <v>4.939</v>
       </c>
       <c r="T16" t="n">
-        <v>3.446</v>
+        <v>5.618</v>
       </c>
       <c r="U16" t="n">
-        <v>1.188</v>
+        <v>1.224</v>
       </c>
     </row>
     <row r="17">
@@ -1536,43 +1536,43 @@
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>0.045</v>
+        <v>0.277</v>
       </c>
       <c r="J17" t="n">
-        <v>0.6890000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="K17" t="n">
-        <v>1.544</v>
+        <v>0.136</v>
       </c>
       <c r="L17" t="n">
-        <v>3.12</v>
+        <v>7.692</v>
       </c>
       <c r="M17" t="n">
-        <v>6.536</v>
+        <v>5.868</v>
       </c>
       <c r="N17" t="n">
-        <v>8.643000000000001</v>
+        <v>13.318</v>
       </c>
       <c r="O17" t="n">
-        <v>12.069</v>
+        <v>11.85</v>
       </c>
       <c r="P17" t="n">
-        <v>15.285</v>
+        <v>10.692</v>
       </c>
       <c r="Q17" t="n">
-        <v>15.906</v>
+        <v>12.864</v>
       </c>
       <c r="R17" t="n">
-        <v>16.792</v>
+        <v>14.591</v>
       </c>
       <c r="S17" t="n">
-        <v>9.539999999999999</v>
+        <v>8.456</v>
       </c>
       <c r="T17" t="n">
-        <v>6.502</v>
+        <v>10.007</v>
       </c>
       <c r="U17" t="n">
-        <v>3.329</v>
+        <v>3.539</v>
       </c>
     </row>
     <row r="18">
@@ -1601,43 +1601,43 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>0.002</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="J18" t="n">
-        <v>0.114</v>
+        <v>0.263</v>
       </c>
       <c r="K18" t="n">
-        <v>0.756</v>
+        <v>0.003</v>
       </c>
       <c r="L18" t="n">
-        <v>1.76</v>
+        <v>5.117</v>
       </c>
       <c r="M18" t="n">
-        <v>4.601999999999999</v>
+        <v>3.262</v>
       </c>
       <c r="N18" t="n">
-        <v>6.574000000000001</v>
+        <v>10.908</v>
       </c>
       <c r="O18" t="n">
-        <v>11.187</v>
+        <v>8.537000000000001</v>
       </c>
       <c r="P18" t="n">
-        <v>14.006</v>
+        <v>6.944</v>
       </c>
       <c r="Q18" t="n">
-        <v>10.872</v>
+        <v>10.49</v>
       </c>
       <c r="R18" t="n">
-        <v>17.675</v>
+        <v>17.161</v>
       </c>
       <c r="S18" t="n">
-        <v>14.093</v>
+        <v>12.808</v>
       </c>
       <c r="T18" t="n">
-        <v>10.938</v>
+        <v>16.635</v>
       </c>
       <c r="U18" t="n">
-        <v>7.420999999999999</v>
+        <v>7.802</v>
       </c>
     </row>
     <row r="19">
@@ -1666,43 +1666,43 @@
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>0.006999999999999999</v>
       </c>
       <c r="J19" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="K19" t="n">
         <v>0.001</v>
       </c>
-      <c r="K19" t="n">
-        <v>0.121</v>
-      </c>
       <c r="L19" t="n">
-        <v>0.5760000000000001</v>
+        <v>3.147</v>
       </c>
       <c r="M19" t="n">
-        <v>1.879</v>
+        <v>1.451</v>
       </c>
       <c r="N19" t="n">
-        <v>3.919</v>
+        <v>7.519000000000001</v>
       </c>
       <c r="O19" t="n">
-        <v>6.551</v>
+        <v>5.69</v>
       </c>
       <c r="P19" t="n">
-        <v>10.75</v>
+        <v>3.514</v>
       </c>
       <c r="Q19" t="n">
-        <v>6.635000000000001</v>
+        <v>6.483</v>
       </c>
       <c r="R19" t="n">
-        <v>12.479</v>
+        <v>17.076</v>
       </c>
       <c r="S19" t="n">
-        <v>21.575</v>
+        <v>18.154</v>
       </c>
       <c r="T19" t="n">
-        <v>19.927</v>
+        <v>22.395</v>
       </c>
       <c r="U19" t="n">
-        <v>15.587</v>
+        <v>14.511</v>
       </c>
     </row>
     <row r="20">
@@ -1731,43 +1731,43 @@
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="K20" t="n">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0.052</v>
+        <v>1.565</v>
       </c>
       <c r="M20" t="n">
-        <v>0.448</v>
+        <v>0.394</v>
       </c>
       <c r="N20" t="n">
-        <v>2.194</v>
+        <v>4.130000000000001</v>
       </c>
       <c r="O20" t="n">
-        <v>2.879</v>
+        <v>2.919</v>
       </c>
       <c r="P20" t="n">
-        <v>5.963</v>
+        <v>1.226</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.388</v>
+        <v>2.784</v>
       </c>
       <c r="R20" t="n">
-        <v>6.871</v>
+        <v>13.847</v>
       </c>
       <c r="S20" t="n">
-        <v>22.962</v>
+        <v>24.086</v>
       </c>
       <c r="T20" t="n">
-        <v>27.165</v>
+        <v>24.904</v>
       </c>
       <c r="U20" t="n">
-        <v>28.073</v>
+        <v>24.142</v>
       </c>
     </row>
     <row r="21">
@@ -1805,34 +1805,34 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>0.003</v>
+        <v>0.263</v>
       </c>
       <c r="M21" t="n">
-        <v>0.048</v>
+        <v>0.042</v>
       </c>
       <c r="N21" t="n">
-        <v>0.491</v>
+        <v>1.223</v>
       </c>
       <c r="O21" t="n">
-        <v>0.7799999999999999</v>
+        <v>0.7060000000000001</v>
       </c>
       <c r="P21" t="n">
-        <v>2.155</v>
+        <v>0.141</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.8789999999999999</v>
+        <v>0.517</v>
       </c>
       <c r="R21" t="n">
-        <v>2.106</v>
+        <v>5.995</v>
       </c>
       <c r="S21" t="n">
-        <v>19.122</v>
+        <v>26.691</v>
       </c>
       <c r="T21" t="n">
-        <v>30.275</v>
+        <v>16.071</v>
       </c>
       <c r="U21" t="n">
-        <v>44.14100000000001</v>
+        <v>48.351</v>
       </c>
     </row>
   </sheetData>

--- a/Resultados.xlsx
+++ b/Resultados.xlsx
@@ -471,34 +471,34 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>Águilas Doradas</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>Internacional de Bogotá</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Millonarios</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Llaneros</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Atlético Bucaramanga</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Santa Fe</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Águilas Doradas</t>
-        </is>
-      </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Independiente Medellín</t>
@@ -516,12 +516,12 @@
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
+          <t>Alianza Valledupar</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
           <t>Jaguares</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Alianza Valledupar</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
@@ -540,34 +540,34 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>23.546</v>
+        <v>26.905</v>
       </c>
       <c r="C2" t="n">
-        <v>31.399</v>
+        <v>34.223</v>
       </c>
       <c r="D2" t="n">
-        <v>20.315</v>
+        <v>21.285</v>
       </c>
       <c r="E2" t="n">
-        <v>11.413</v>
+        <v>13.737</v>
       </c>
       <c r="F2" t="n">
-        <v>5.964</v>
+        <v>2.965</v>
       </c>
       <c r="G2" t="n">
-        <v>4.94</v>
+        <v>0.628</v>
       </c>
       <c r="H2" t="n">
-        <v>2.211</v>
+        <v>0.221</v>
       </c>
       <c r="I2" t="n">
-        <v>0.168</v>
+        <v>0.035</v>
       </c>
       <c r="J2" t="n">
-        <v>0.04</v>
+        <v>0.001</v>
       </c>
       <c r="K2" t="n">
-        <v>0.004</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -605,37 +605,37 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>20.054</v>
+        <v>22.548</v>
       </c>
       <c r="C3" t="n">
-        <v>19.559</v>
+        <v>25.519</v>
       </c>
       <c r="D3" t="n">
-        <v>17.539</v>
+        <v>23.185</v>
       </c>
       <c r="E3" t="n">
-        <v>13.961</v>
+        <v>17.612</v>
       </c>
       <c r="F3" t="n">
-        <v>9.045</v>
+        <v>6.539000000000001</v>
       </c>
       <c r="G3" t="n">
-        <v>11.55</v>
+        <v>2.836</v>
       </c>
       <c r="H3" t="n">
-        <v>6.925000000000001</v>
+        <v>1.326</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9900000000000001</v>
+        <v>0.388</v>
       </c>
       <c r="J3" t="n">
-        <v>0.303</v>
+        <v>0.044</v>
       </c>
       <c r="K3" t="n">
-        <v>0.073</v>
+        <v>0.003</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -670,40 +670,40 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>14.735</v>
+        <v>18.58</v>
       </c>
       <c r="C4" t="n">
-        <v>14.765</v>
+        <v>18.032</v>
       </c>
       <c r="D4" t="n">
-        <v>15.069</v>
+        <v>21.624</v>
       </c>
       <c r="E4" t="n">
-        <v>14.132</v>
+        <v>19.434</v>
       </c>
       <c r="F4" t="n">
-        <v>11.398</v>
+        <v>9.796000000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>14.72</v>
+        <v>6.414000000000001</v>
       </c>
       <c r="H4" t="n">
-        <v>10.544</v>
+        <v>3.891</v>
       </c>
       <c r="I4" t="n">
-        <v>2.786</v>
+        <v>1.73</v>
       </c>
       <c r="J4" t="n">
-        <v>1.241</v>
+        <v>0.404</v>
       </c>
       <c r="K4" t="n">
-        <v>0.604</v>
+        <v>0.091</v>
       </c>
       <c r="L4" t="n">
-        <v>0.005</v>
+        <v>0.004</v>
       </c>
       <c r="M4" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -735,43 +735,43 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>12.102</v>
+        <v>15.182</v>
       </c>
       <c r="C5" t="n">
-        <v>11.531</v>
+        <v>11.406</v>
       </c>
       <c r="D5" t="n">
-        <v>12.728</v>
+        <v>15.119</v>
       </c>
       <c r="E5" t="n">
-        <v>13.513</v>
+        <v>18.575</v>
       </c>
       <c r="F5" t="n">
-        <v>12.811</v>
+        <v>13.779</v>
       </c>
       <c r="G5" t="n">
-        <v>15.269</v>
+        <v>10.977</v>
       </c>
       <c r="H5" t="n">
-        <v>12.097</v>
+        <v>7.382</v>
       </c>
       <c r="I5" t="n">
-        <v>4.87</v>
+        <v>4.752</v>
       </c>
       <c r="J5" t="n">
-        <v>2.752</v>
+        <v>2.062</v>
       </c>
       <c r="K5" t="n">
-        <v>2.255</v>
+        <v>0.629</v>
       </c>
       <c r="L5" t="n">
-        <v>0.044</v>
+        <v>0.133</v>
       </c>
       <c r="M5" t="n">
-        <v>0.027</v>
+        <v>0.004</v>
       </c>
       <c r="N5" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -800,43 +800,43 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>9.988</v>
+        <v>9.125999999999999</v>
       </c>
       <c r="C6" t="n">
-        <v>8.529</v>
+        <v>6.555999999999999</v>
       </c>
       <c r="D6" t="n">
-        <v>10.772</v>
+        <v>9.690999999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>12.57</v>
+        <v>13.321</v>
       </c>
       <c r="F6" t="n">
-        <v>13.281</v>
+        <v>16.911</v>
       </c>
       <c r="G6" t="n">
-        <v>14.404</v>
+        <v>15.971</v>
       </c>
       <c r="H6" t="n">
-        <v>13.519</v>
+        <v>11.842</v>
       </c>
       <c r="I6" t="n">
-        <v>6.869</v>
+        <v>8.308</v>
       </c>
       <c r="J6" t="n">
-        <v>4.414</v>
+        <v>4.643</v>
       </c>
       <c r="K6" t="n">
-        <v>5.256</v>
+        <v>2.425</v>
       </c>
       <c r="L6" t="n">
-        <v>0.227</v>
+        <v>1.072</v>
       </c>
       <c r="M6" t="n">
-        <v>0.166</v>
+        <v>0.117</v>
       </c>
       <c r="N6" t="n">
-        <v>0.005</v>
+        <v>0.017</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -865,49 +865,49 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>7.613</v>
+        <v>4.821000000000001</v>
       </c>
       <c r="C7" t="n">
-        <v>6.254999999999999</v>
+        <v>3.066</v>
       </c>
       <c r="D7" t="n">
-        <v>8.888</v>
+        <v>5.36</v>
       </c>
       <c r="E7" t="n">
-        <v>11.23</v>
+        <v>8.975</v>
       </c>
       <c r="F7" t="n">
-        <v>12.86</v>
+        <v>16.416</v>
       </c>
       <c r="G7" t="n">
-        <v>12.411</v>
+        <v>16.315</v>
       </c>
       <c r="H7" t="n">
-        <v>14.314</v>
+        <v>15.004</v>
       </c>
       <c r="I7" t="n">
-        <v>9.539999999999999</v>
+        <v>11.773</v>
       </c>
       <c r="J7" t="n">
-        <v>6.638</v>
+        <v>8.27</v>
       </c>
       <c r="K7" t="n">
-        <v>8.473000000000001</v>
+        <v>5.649</v>
       </c>
       <c r="L7" t="n">
-        <v>0.8630000000000001</v>
+        <v>3.27</v>
       </c>
       <c r="M7" t="n">
-        <v>0.843</v>
+        <v>0.831</v>
       </c>
       <c r="N7" t="n">
-        <v>0.062</v>
+        <v>0.238</v>
       </c>
       <c r="O7" t="n">
-        <v>0.01</v>
+        <v>0.008</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>0.004</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -930,52 +930,52 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>5.518</v>
+        <v>1.841</v>
       </c>
       <c r="C8" t="n">
-        <v>4.170999999999999</v>
+        <v>0.984</v>
       </c>
       <c r="D8" t="n">
-        <v>6.406000000000001</v>
+        <v>2.33</v>
       </c>
       <c r="E8" t="n">
-        <v>9.131</v>
+        <v>4.534</v>
       </c>
       <c r="F8" t="n">
-        <v>11.622</v>
+        <v>12.571</v>
       </c>
       <c r="G8" t="n">
-        <v>10.256</v>
+        <v>14.729</v>
       </c>
       <c r="H8" t="n">
-        <v>13.519</v>
+        <v>15.555</v>
       </c>
       <c r="I8" t="n">
-        <v>12.55</v>
+        <v>14.67</v>
       </c>
       <c r="J8" t="n">
-        <v>9.754999999999999</v>
+        <v>12.975</v>
       </c>
       <c r="K8" t="n">
-        <v>12.043</v>
+        <v>9.153</v>
       </c>
       <c r="L8" t="n">
-        <v>2.074</v>
+        <v>6.138</v>
       </c>
       <c r="M8" t="n">
-        <v>2.57</v>
+        <v>2.898</v>
       </c>
       <c r="N8" t="n">
-        <v>0.269</v>
+        <v>1.42</v>
       </c>
       <c r="O8" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.136</v>
       </c>
       <c r="P8" t="n">
-        <v>0.026</v>
+        <v>0.057</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.003</v>
+        <v>0.009000000000000001</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -995,55 +995,55 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>3.307</v>
+        <v>0.666</v>
       </c>
       <c r="C9" t="n">
-        <v>2.292</v>
+        <v>0.201</v>
       </c>
       <c r="D9" t="n">
-        <v>4.355</v>
+        <v>1.064</v>
       </c>
       <c r="E9" t="n">
-        <v>6.35</v>
+        <v>2.259</v>
       </c>
       <c r="F9" t="n">
-        <v>9.157999999999999</v>
+        <v>8.788</v>
       </c>
       <c r="G9" t="n">
-        <v>7.819</v>
+        <v>11.749</v>
       </c>
       <c r="H9" t="n">
-        <v>11.342</v>
+        <v>13.682</v>
       </c>
       <c r="I9" t="n">
-        <v>14.28</v>
+        <v>14.868</v>
       </c>
       <c r="J9" t="n">
-        <v>13.078</v>
+        <v>14.814</v>
       </c>
       <c r="K9" t="n">
-        <v>16.211</v>
+        <v>12.251</v>
       </c>
       <c r="L9" t="n">
-        <v>4.119</v>
+        <v>8.824999999999999</v>
       </c>
       <c r="M9" t="n">
-        <v>5.508</v>
+        <v>5.758</v>
       </c>
       <c r="N9" t="n">
-        <v>1.064</v>
+        <v>3.881</v>
       </c>
       <c r="O9" t="n">
-        <v>0.662</v>
+        <v>0.5930000000000001</v>
       </c>
       <c r="P9" t="n">
-        <v>0.379</v>
+        <v>0.472</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.076</v>
+        <v>0.119</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -1060,58 +1060,58 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>1.806</v>
+        <v>0.262</v>
       </c>
       <c r="C10" t="n">
-        <v>0.9740000000000001</v>
+        <v>0.01</v>
       </c>
       <c r="D10" t="n">
-        <v>2.439</v>
+        <v>0.309</v>
       </c>
       <c r="E10" t="n">
-        <v>4.299</v>
+        <v>1.224</v>
       </c>
       <c r="F10" t="n">
-        <v>6.587999999999999</v>
+        <v>5.747</v>
       </c>
       <c r="G10" t="n">
-        <v>4.962</v>
+        <v>8.353</v>
       </c>
       <c r="H10" t="n">
-        <v>8.227</v>
+        <v>11.243</v>
       </c>
       <c r="I10" t="n">
-        <v>14.531</v>
+        <v>13.717</v>
       </c>
       <c r="J10" t="n">
-        <v>15.043</v>
+        <v>14.549</v>
       </c>
       <c r="K10" t="n">
-        <v>17.932</v>
+        <v>13.97</v>
       </c>
       <c r="L10" t="n">
-        <v>6.875000000000001</v>
+        <v>11.389</v>
       </c>
       <c r="M10" t="n">
-        <v>8.225</v>
+        <v>8.815000000000001</v>
       </c>
       <c r="N10" t="n">
-        <v>2.679</v>
+        <v>6.374000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>2.516</v>
+        <v>1.539</v>
       </c>
       <c r="P10" t="n">
-        <v>2.311</v>
+        <v>1.517</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.5720000000000001</v>
+        <v>0.843</v>
       </c>
       <c r="R10" t="n">
-        <v>0.02</v>
+        <v>0.13</v>
       </c>
       <c r="S10" t="n">
-        <v>0.001</v>
+        <v>0.009000000000000001</v>
       </c>
       <c r="T10" t="n">
         <v>0</v>
@@ -1125,58 +1125,58 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>0.876</v>
+        <v>0.064</v>
       </c>
       <c r="C11" t="n">
-        <v>0.4349999999999999</v>
+        <v>0.003</v>
       </c>
       <c r="D11" t="n">
-        <v>1.099</v>
+        <v>0.032</v>
       </c>
       <c r="E11" t="n">
-        <v>2.234</v>
+        <v>0.304</v>
       </c>
       <c r="F11" t="n">
-        <v>4.36</v>
+        <v>3.47</v>
       </c>
       <c r="G11" t="n">
-        <v>2.645</v>
+        <v>5.787</v>
       </c>
       <c r="H11" t="n">
-        <v>4.523</v>
+        <v>8.081000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>12.996</v>
+        <v>10.93</v>
       </c>
       <c r="J11" t="n">
-        <v>15.012</v>
+        <v>13.08</v>
       </c>
       <c r="K11" t="n">
-        <v>14.492</v>
+        <v>13.833</v>
       </c>
       <c r="L11" t="n">
-        <v>9.944000000000001</v>
+        <v>13.391</v>
       </c>
       <c r="M11" t="n">
-        <v>11.315</v>
+        <v>12.081</v>
       </c>
       <c r="N11" t="n">
-        <v>4.99</v>
+        <v>8.773999999999999</v>
       </c>
       <c r="O11" t="n">
-        <v>5.521</v>
+        <v>2.911</v>
       </c>
       <c r="P11" t="n">
-        <v>6.630999999999999</v>
+        <v>3.35</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.704</v>
+        <v>3.173</v>
       </c>
       <c r="R11" t="n">
-        <v>0.209</v>
+        <v>0.594</v>
       </c>
       <c r="S11" t="n">
-        <v>0.012</v>
+        <v>0.14</v>
       </c>
       <c r="T11" t="n">
         <v>0.002</v>
@@ -1190,64 +1190,64 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>0.289</v>
+        <v>0.005</v>
       </c>
       <c r="C12" t="n">
-        <v>0.08800000000000001</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>0.321</v>
+        <v>0.001</v>
       </c>
       <c r="E12" t="n">
-        <v>0.8200000000000001</v>
+        <v>0.025</v>
       </c>
       <c r="F12" t="n">
-        <v>1.793</v>
+        <v>1.833</v>
       </c>
       <c r="G12" t="n">
-        <v>0.876</v>
+        <v>3.432</v>
       </c>
       <c r="H12" t="n">
-        <v>1.962</v>
+        <v>5.758</v>
       </c>
       <c r="I12" t="n">
-        <v>8.685</v>
+        <v>7.614999999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>11.827</v>
+        <v>10.509</v>
       </c>
       <c r="K12" t="n">
-        <v>10.603</v>
+        <v>12.363</v>
       </c>
       <c r="L12" t="n">
-        <v>12.272</v>
+        <v>13.699</v>
       </c>
       <c r="M12" t="n">
-        <v>13.316</v>
+        <v>13.873</v>
       </c>
       <c r="N12" t="n">
-        <v>7.847</v>
+        <v>10.982</v>
       </c>
       <c r="O12" t="n">
-        <v>9.025</v>
+        <v>4.636</v>
       </c>
       <c r="P12" t="n">
-        <v>11.842</v>
+        <v>5.567</v>
       </c>
       <c r="Q12" t="n">
-        <v>6.957000000000001</v>
+        <v>6.895</v>
       </c>
       <c r="R12" t="n">
-        <v>1.305</v>
+        <v>1.674</v>
       </c>
       <c r="S12" t="n">
-        <v>0.133</v>
+        <v>1.108</v>
       </c>
       <c r="T12" t="n">
-        <v>0.039</v>
+        <v>0.021</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>0.004</v>
       </c>
     </row>
     <row r="13">
@@ -1255,64 +1255,64 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>0.137</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>0.067</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>0.293</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>0.707</v>
+        <v>0.771</v>
       </c>
       <c r="G13" t="n">
-        <v>0.141</v>
+        <v>1.735</v>
       </c>
       <c r="H13" t="n">
-        <v>0.718</v>
+        <v>3.333</v>
       </c>
       <c r="I13" t="n">
-        <v>5.737</v>
+        <v>5.056</v>
       </c>
       <c r="J13" t="n">
-        <v>8.433999999999999</v>
+        <v>7.460999999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>6.383</v>
+        <v>10.292</v>
       </c>
       <c r="L13" t="n">
-        <v>12.679</v>
+        <v>12.858</v>
       </c>
       <c r="M13" t="n">
-        <v>14.243</v>
+        <v>13.237</v>
       </c>
       <c r="N13" t="n">
-        <v>9.635999999999999</v>
+        <v>12.293</v>
       </c>
       <c r="O13" t="n">
-        <v>11.737</v>
+        <v>7.038</v>
       </c>
       <c r="P13" t="n">
-        <v>13.709</v>
+        <v>8.273</v>
       </c>
       <c r="Q13" t="n">
-        <v>11.083</v>
+        <v>10.445</v>
       </c>
       <c r="R13" t="n">
-        <v>3.468</v>
+        <v>3.342</v>
       </c>
       <c r="S13" t="n">
-        <v>0.5369999999999999</v>
+        <v>3.601</v>
       </c>
       <c r="T13" t="n">
-        <v>0.283</v>
+        <v>0.221</v>
       </c>
       <c r="U13" t="n">
-        <v>0.006</v>
+        <v>0.044</v>
       </c>
     </row>
     <row r="14">
@@ -1320,64 +1320,64 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>0.028</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>0.052</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>0.338</v>
+        <v>0.321</v>
       </c>
       <c r="G14" t="n">
-        <v>0.006999999999999999</v>
+        <v>0.6930000000000001</v>
       </c>
       <c r="H14" t="n">
-        <v>0.094</v>
+        <v>1.637</v>
       </c>
       <c r="I14" t="n">
-        <v>3.469</v>
+        <v>3.211</v>
       </c>
       <c r="J14" t="n">
-        <v>5.423</v>
+        <v>5.069</v>
       </c>
       <c r="K14" t="n">
-        <v>3.108</v>
+        <v>7.753</v>
       </c>
       <c r="L14" t="n">
-        <v>12.492</v>
+        <v>10.552</v>
       </c>
       <c r="M14" t="n">
-        <v>12.87</v>
+        <v>11.711</v>
       </c>
       <c r="N14" t="n">
-        <v>11.196</v>
+        <v>12.506</v>
       </c>
       <c r="O14" t="n">
-        <v>13.556</v>
+        <v>9.232999999999999</v>
       </c>
       <c r="P14" t="n">
-        <v>15.572</v>
+        <v>10.697</v>
       </c>
       <c r="Q14" t="n">
-        <v>13.523</v>
+        <v>13.383</v>
       </c>
       <c r="R14" t="n">
-        <v>5.827</v>
+        <v>5.25</v>
       </c>
       <c r="S14" t="n">
-        <v>1.336</v>
+        <v>6.898</v>
       </c>
       <c r="T14" t="n">
-        <v>1.048</v>
+        <v>0.598</v>
       </c>
       <c r="U14" t="n">
-        <v>0.059</v>
+        <v>0.488</v>
       </c>
     </row>
     <row r="15">
@@ -1385,7 +1385,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
@@ -1394,55 +1394,55 @@
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>0.06899999999999999</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>0.303</v>
       </c>
       <c r="H15" t="n">
-        <v>0.005</v>
+        <v>0.726</v>
       </c>
       <c r="I15" t="n">
-        <v>1.546</v>
+        <v>1.63</v>
       </c>
       <c r="J15" t="n">
-        <v>3.404</v>
+        <v>3.17</v>
       </c>
       <c r="K15" t="n">
-        <v>1.728</v>
+        <v>5.061</v>
       </c>
       <c r="L15" t="n">
-        <v>11.077</v>
+        <v>7.255000000000001</v>
       </c>
       <c r="M15" t="n">
-        <v>11.072</v>
+        <v>9.927</v>
       </c>
       <c r="N15" t="n">
-        <v>12.136</v>
+        <v>11.825</v>
       </c>
       <c r="O15" t="n">
-        <v>13.705</v>
+        <v>10.905</v>
       </c>
       <c r="P15" t="n">
-        <v>14.398</v>
+        <v>12.72</v>
       </c>
       <c r="Q15" t="n">
-        <v>15.954</v>
+        <v>15.138</v>
       </c>
       <c r="R15" t="n">
-        <v>8.692</v>
+        <v>7.697</v>
       </c>
       <c r="S15" t="n">
-        <v>2.847</v>
+        <v>9.852</v>
       </c>
       <c r="T15" t="n">
-        <v>2.998</v>
+        <v>1.433</v>
       </c>
       <c r="U15" t="n">
-        <v>0.366</v>
+        <v>2.271</v>
       </c>
     </row>
     <row r="16">
@@ -1462,52 +1462,52 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>0.006</v>
+        <v>0.005</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>0.075</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>0.27</v>
       </c>
       <c r="I16" t="n">
-        <v>0.628</v>
+        <v>0.8059999999999999</v>
       </c>
       <c r="J16" t="n">
-        <v>1.609</v>
+        <v>1.656</v>
       </c>
       <c r="K16" t="n">
-        <v>0.695</v>
+        <v>3.336</v>
       </c>
       <c r="L16" t="n">
-        <v>9.544</v>
+        <v>4.891999999999999</v>
       </c>
       <c r="M16" t="n">
-        <v>8.827</v>
+        <v>7.681</v>
       </c>
       <c r="N16" t="n">
-        <v>13.017</v>
+        <v>11.021</v>
       </c>
       <c r="O16" t="n">
-        <v>13.479</v>
+        <v>11.649</v>
       </c>
       <c r="P16" t="n">
-        <v>12.615</v>
+        <v>13.188</v>
       </c>
       <c r="Q16" t="n">
-        <v>15.99</v>
+        <v>13.981</v>
       </c>
       <c r="R16" t="n">
-        <v>11.809</v>
+        <v>10.396</v>
       </c>
       <c r="S16" t="n">
-        <v>4.939</v>
+        <v>12.63</v>
       </c>
       <c r="T16" t="n">
-        <v>5.618</v>
+        <v>2.593</v>
       </c>
       <c r="U16" t="n">
-        <v>1.224</v>
+        <v>5.821</v>
       </c>
     </row>
     <row r="17">
@@ -1527,52 +1527,52 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>0.003</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>0.047</v>
       </c>
       <c r="I17" t="n">
-        <v>0.277</v>
+        <v>0.396</v>
       </c>
       <c r="J17" t="n">
-        <v>0.7100000000000001</v>
+        <v>0.7779999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>0.136</v>
+        <v>1.869</v>
       </c>
       <c r="L17" t="n">
-        <v>7.692</v>
+        <v>3.330000000000001</v>
       </c>
       <c r="M17" t="n">
-        <v>5.868</v>
+        <v>5.419</v>
       </c>
       <c r="N17" t="n">
-        <v>13.318</v>
+        <v>8.35</v>
       </c>
       <c r="O17" t="n">
-        <v>11.85</v>
+        <v>12.14</v>
       </c>
       <c r="P17" t="n">
-        <v>10.692</v>
+        <v>12.731</v>
       </c>
       <c r="Q17" t="n">
-        <v>12.864</v>
+        <v>11.954</v>
       </c>
       <c r="R17" t="n">
-        <v>14.591</v>
+        <v>12.942</v>
       </c>
       <c r="S17" t="n">
-        <v>8.456</v>
+        <v>15.255</v>
       </c>
       <c r="T17" t="n">
-        <v>10.007</v>
+        <v>4.449</v>
       </c>
       <c r="U17" t="n">
-        <v>3.539</v>
+        <v>10.336</v>
       </c>
     </row>
     <row r="18">
@@ -1598,46 +1598,46 @@
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="I18" t="n">
-        <v>0.06999999999999999</v>
+        <v>0.108</v>
       </c>
       <c r="J18" t="n">
-        <v>0.263</v>
+        <v>0.378</v>
       </c>
       <c r="K18" t="n">
-        <v>0.003</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="L18" t="n">
-        <v>5.117</v>
+        <v>1.853</v>
       </c>
       <c r="M18" t="n">
-        <v>3.262</v>
+        <v>3.859</v>
       </c>
       <c r="N18" t="n">
-        <v>10.908</v>
+        <v>5.936</v>
       </c>
       <c r="O18" t="n">
-        <v>8.537000000000001</v>
+        <v>11.815</v>
       </c>
       <c r="P18" t="n">
-        <v>6.944</v>
+        <v>11.65</v>
       </c>
       <c r="Q18" t="n">
-        <v>10.49</v>
+        <v>10.413</v>
       </c>
       <c r="R18" t="n">
-        <v>17.161</v>
+        <v>14.506</v>
       </c>
       <c r="S18" t="n">
-        <v>12.808</v>
+        <v>16.337</v>
       </c>
       <c r="T18" t="n">
-        <v>16.635</v>
+        <v>7.242999999999999</v>
       </c>
       <c r="U18" t="n">
-        <v>7.802</v>
+        <v>15.082</v>
       </c>
     </row>
     <row r="19">
@@ -1669,40 +1669,40 @@
         <v>0.006999999999999999</v>
       </c>
       <c r="J19" t="n">
-        <v>0.052</v>
+        <v>0.118</v>
       </c>
       <c r="K19" t="n">
-        <v>0.001</v>
+        <v>0.392</v>
       </c>
       <c r="L19" t="n">
-        <v>3.147</v>
+        <v>0.9169999999999999</v>
       </c>
       <c r="M19" t="n">
-        <v>1.451</v>
+        <v>2.389</v>
       </c>
       <c r="N19" t="n">
-        <v>7.519000000000001</v>
+        <v>3.918</v>
       </c>
       <c r="O19" t="n">
-        <v>5.69</v>
+        <v>10.849</v>
       </c>
       <c r="P19" t="n">
-        <v>3.514</v>
+        <v>9.638</v>
       </c>
       <c r="Q19" t="n">
-        <v>6.483</v>
+        <v>7.913</v>
       </c>
       <c r="R19" t="n">
-        <v>17.076</v>
+        <v>15.723</v>
       </c>
       <c r="S19" t="n">
-        <v>18.154</v>
+        <v>15.376</v>
       </c>
       <c r="T19" t="n">
-        <v>22.395</v>
+        <v>11.328</v>
       </c>
       <c r="U19" t="n">
-        <v>14.511</v>
+        <v>21.432</v>
       </c>
     </row>
     <row r="20">
@@ -1731,43 +1731,43 @@
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>0.002</v>
+        <v>0.018</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>0.106</v>
       </c>
       <c r="L20" t="n">
-        <v>1.565</v>
+        <v>0.351</v>
       </c>
       <c r="M20" t="n">
-        <v>0.394</v>
+        <v>1.034</v>
       </c>
       <c r="N20" t="n">
-        <v>4.130000000000001</v>
+        <v>1.923</v>
       </c>
       <c r="O20" t="n">
-        <v>2.919</v>
+        <v>9.682</v>
       </c>
       <c r="P20" t="n">
-        <v>1.226</v>
+        <v>7.029000000000001</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.784</v>
+        <v>4.444</v>
       </c>
       <c r="R20" t="n">
-        <v>13.847</v>
+        <v>16.402</v>
       </c>
       <c r="S20" t="n">
-        <v>24.086</v>
+        <v>12.547</v>
       </c>
       <c r="T20" t="n">
-        <v>24.904</v>
+        <v>19.158</v>
       </c>
       <c r="U20" t="n">
-        <v>24.142</v>
+        <v>27.306</v>
       </c>
     </row>
     <row r="21">
@@ -1799,40 +1799,40 @@
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>0.006</v>
       </c>
       <c r="L21" t="n">
-        <v>0.263</v>
+        <v>0.07100000000000001</v>
       </c>
       <c r="M21" t="n">
-        <v>0.042</v>
+        <v>0.366</v>
       </c>
       <c r="N21" t="n">
-        <v>1.223</v>
+        <v>0.542</v>
       </c>
       <c r="O21" t="n">
-        <v>0.7060000000000001</v>
+        <v>6.866</v>
       </c>
       <c r="P21" t="n">
-        <v>0.141</v>
+        <v>3.107</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.517</v>
+        <v>1.29</v>
       </c>
       <c r="R21" t="n">
-        <v>5.995</v>
+        <v>11.334</v>
       </c>
       <c r="S21" t="n">
-        <v>26.691</v>
+        <v>6.247</v>
       </c>
       <c r="T21" t="n">
-        <v>16.071</v>
+        <v>52.954</v>
       </c>
       <c r="U21" t="n">
-        <v>48.351</v>
+        <v>17.216</v>
       </c>
     </row>
   </sheetData>

--- a/Resultados.xlsx
+++ b/Resultados.xlsx
@@ -446,62 +446,62 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>Junior</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Deportes Tolima</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>América de Cali</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Once Caldas</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Junior</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>América de Cali</t>
-        </is>
-      </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>Internacional de Bogotá</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Santa Fe</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>Deportivo Cali</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Independiente Medellín</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Millonarios</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Águilas Doradas</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Internacional de Bogotá</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Millonarios</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Llaneros</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Atlético Bucaramanga</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Santa Fe</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>Independiente Medellín</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
@@ -540,31 +540,31 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>26.905</v>
+        <v>55.97299999999999</v>
       </c>
       <c r="C2" t="n">
-        <v>34.223</v>
+        <v>33.093</v>
       </c>
       <c r="D2" t="n">
-        <v>21.285</v>
+        <v>10.934</v>
       </c>
       <c r="E2" t="n">
-        <v>13.737</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>2.965</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0.628</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0.221</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>0.035</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -605,34 +605,34 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>22.548</v>
+        <v>25.767</v>
       </c>
       <c r="C3" t="n">
-        <v>25.519</v>
+        <v>33.733</v>
       </c>
       <c r="D3" t="n">
-        <v>23.185</v>
+        <v>29.574</v>
       </c>
       <c r="E3" t="n">
-        <v>17.612</v>
+        <v>10.926</v>
       </c>
       <c r="F3" t="n">
-        <v>6.539000000000001</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>2.836</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>1.326</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0.388</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0.044</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>0.003</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -670,37 +670,37 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>18.58</v>
+        <v>14.549</v>
       </c>
       <c r="C4" t="n">
-        <v>18.032</v>
+        <v>7.327999999999999</v>
       </c>
       <c r="D4" t="n">
-        <v>21.624</v>
+        <v>21.292</v>
       </c>
       <c r="E4" t="n">
-        <v>19.434</v>
+        <v>37.155</v>
       </c>
       <c r="F4" t="n">
-        <v>9.796000000000001</v>
+        <v>17.19</v>
       </c>
       <c r="G4" t="n">
-        <v>6.414000000000001</v>
+        <v>2.486</v>
       </c>
       <c r="H4" t="n">
-        <v>3.891</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0.404</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0.091</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0.004</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -735,40 +735,40 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>15.182</v>
+        <v>3.711</v>
       </c>
       <c r="C5" t="n">
-        <v>11.406</v>
+        <v>18.426</v>
       </c>
       <c r="D5" t="n">
-        <v>15.119</v>
+        <v>18.582</v>
       </c>
       <c r="E5" t="n">
-        <v>18.575</v>
+        <v>17.466</v>
       </c>
       <c r="F5" t="n">
-        <v>13.779</v>
+        <v>26.023</v>
       </c>
       <c r="G5" t="n">
-        <v>10.977</v>
+        <v>13.31</v>
       </c>
       <c r="H5" t="n">
-        <v>7.382</v>
+        <v>2.482</v>
       </c>
       <c r="I5" t="n">
-        <v>4.752</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>2.062</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0.629</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>0.133</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>0.004</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -800,43 +800,43 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>9.125999999999999</v>
+        <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>6.555999999999999</v>
+        <v>7.42</v>
       </c>
       <c r="D6" t="n">
-        <v>9.690999999999999</v>
+        <v>14.772</v>
       </c>
       <c r="E6" t="n">
-        <v>13.321</v>
+        <v>14.902</v>
       </c>
       <c r="F6" t="n">
-        <v>16.911</v>
+        <v>18.406</v>
       </c>
       <c r="G6" t="n">
-        <v>15.971</v>
+        <v>25.864</v>
       </c>
       <c r="H6" t="n">
-        <v>11.842</v>
+        <v>14.899</v>
       </c>
       <c r="I6" t="n">
-        <v>8.308</v>
+        <v>3.737</v>
       </c>
       <c r="J6" t="n">
-        <v>4.643</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>2.425</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>1.072</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>0.117</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>0.017</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -865,49 +865,49 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>4.821000000000001</v>
+        <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>3.066</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>5.36</v>
+        <v>4.846</v>
       </c>
       <c r="E7" t="n">
-        <v>8.975</v>
+        <v>14.699</v>
       </c>
       <c r="F7" t="n">
-        <v>16.416</v>
+        <v>16.092</v>
       </c>
       <c r="G7" t="n">
-        <v>16.315</v>
+        <v>19.859</v>
       </c>
       <c r="H7" t="n">
-        <v>15.004</v>
+        <v>29.553</v>
       </c>
       <c r="I7" t="n">
-        <v>11.773</v>
+        <v>14.951</v>
       </c>
       <c r="J7" t="n">
-        <v>8.27</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>5.649</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0.831</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>0.238</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>0.008</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>0.004</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -930,52 +930,52 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>1.841</v>
+        <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>0.984</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>4.534</v>
+        <v>4.852</v>
       </c>
       <c r="F8" t="n">
-        <v>12.571</v>
+        <v>22.289</v>
       </c>
       <c r="G8" t="n">
-        <v>14.729</v>
+        <v>19.764</v>
       </c>
       <c r="H8" t="n">
-        <v>15.555</v>
+        <v>19.485</v>
       </c>
       <c r="I8" t="n">
-        <v>14.67</v>
+        <v>22.397</v>
       </c>
       <c r="J8" t="n">
-        <v>12.975</v>
+        <v>11.213</v>
       </c>
       <c r="K8" t="n">
-        <v>9.153</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>6.138</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>2.898</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>0.136</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>0.057</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.009000000000000001</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -995,55 +995,55 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>0.666</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>0.201</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>1.064</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>2.259</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>8.788</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>11.749</v>
+        <v>14.943</v>
       </c>
       <c r="H9" t="n">
-        <v>13.682</v>
+        <v>7.463</v>
       </c>
       <c r="I9" t="n">
-        <v>14.868</v>
+        <v>20.974</v>
       </c>
       <c r="J9" t="n">
-        <v>14.814</v>
+        <v>36.921</v>
       </c>
       <c r="K9" t="n">
-        <v>12.251</v>
+        <v>17.279</v>
       </c>
       <c r="L9" t="n">
-        <v>8.824999999999999</v>
+        <v>2.42</v>
       </c>
       <c r="M9" t="n">
-        <v>5.758</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>3.881</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>0.5930000000000001</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>0.472</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.119</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -1060,58 +1060,58 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>0.262</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>0.309</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>1.224</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>5.747</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>8.353</v>
+        <v>3.774</v>
       </c>
       <c r="H10" t="n">
-        <v>11.243</v>
+        <v>18.668</v>
       </c>
       <c r="I10" t="n">
-        <v>13.717</v>
+        <v>18.193</v>
       </c>
       <c r="J10" t="n">
-        <v>14.549</v>
+        <v>17.461</v>
       </c>
       <c r="K10" t="n">
-        <v>13.97</v>
+        <v>25.71</v>
       </c>
       <c r="L10" t="n">
-        <v>11.389</v>
+        <v>13.648</v>
       </c>
       <c r="M10" t="n">
-        <v>8.815000000000001</v>
+        <v>2.546</v>
       </c>
       <c r="N10" t="n">
-        <v>6.374000000000001</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>1.539</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.517</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.843</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.13</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0.009000000000000001</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
         <v>0</v>
@@ -1125,61 +1125,61 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>0.064</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>0.003</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>0.032</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>0.304</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>5.787</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>8.081000000000001</v>
+        <v>7.449999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>10.93</v>
+        <v>14.813</v>
       </c>
       <c r="J11" t="n">
-        <v>13.08</v>
+        <v>14.684</v>
       </c>
       <c r="K11" t="n">
-        <v>13.833</v>
+        <v>18.612</v>
       </c>
       <c r="L11" t="n">
-        <v>13.391</v>
+        <v>25.952</v>
       </c>
       <c r="M11" t="n">
-        <v>12.081</v>
+        <v>11.136</v>
       </c>
       <c r="N11" t="n">
-        <v>8.773999999999999</v>
+        <v>7.353</v>
       </c>
       <c r="O11" t="n">
-        <v>2.911</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.173</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.594</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0.14</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
@@ -1190,64 +1190,64 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>0.025</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>1.833</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>3.432</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>5.758</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>7.614999999999999</v>
+        <v>4.935</v>
       </c>
       <c r="J12" t="n">
-        <v>10.509</v>
+        <v>14.951</v>
       </c>
       <c r="K12" t="n">
-        <v>12.363</v>
+        <v>8.556999999999999</v>
       </c>
       <c r="L12" t="n">
-        <v>13.699</v>
+        <v>22.322</v>
       </c>
       <c r="M12" t="n">
-        <v>13.873</v>
+        <v>25.651</v>
       </c>
       <c r="N12" t="n">
-        <v>10.982</v>
+        <v>21.086</v>
       </c>
       <c r="O12" t="n">
-        <v>4.636</v>
+        <v>2.498</v>
       </c>
       <c r="P12" t="n">
-        <v>5.567</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>6.895</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.674</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>1.108</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>0.021</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>0.004</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1267,52 +1267,52 @@
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>0.771</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>1.735</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>3.333</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>5.056</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>7.460999999999999</v>
+        <v>4.77</v>
       </c>
       <c r="K13" t="n">
-        <v>10.292</v>
+        <v>14.879</v>
       </c>
       <c r="L13" t="n">
-        <v>12.858</v>
+        <v>15.957</v>
       </c>
       <c r="M13" t="n">
-        <v>13.237</v>
+        <v>27.191</v>
       </c>
       <c r="N13" t="n">
-        <v>12.293</v>
+        <v>18.602</v>
       </c>
       <c r="O13" t="n">
-        <v>7.038</v>
+        <v>11.191</v>
       </c>
       <c r="P13" t="n">
-        <v>8.273</v>
+        <v>7.41</v>
       </c>
       <c r="Q13" t="n">
-        <v>10.445</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>3.342</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>3.601</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>0.221</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>0.044</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1332,52 +1332,52 @@
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>0.321</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>0.6930000000000001</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>1.637</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>3.211</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>5.069</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>7.753</v>
+        <v>14.963</v>
       </c>
       <c r="L14" t="n">
-        <v>10.552</v>
+        <v>14.758</v>
       </c>
       <c r="M14" t="n">
-        <v>11.711</v>
+        <v>3.711</v>
       </c>
       <c r="N14" t="n">
-        <v>12.506</v>
+        <v>17.191</v>
       </c>
       <c r="O14" t="n">
-        <v>9.232999999999999</v>
+        <v>25.898</v>
       </c>
       <c r="P14" t="n">
-        <v>10.697</v>
+        <v>21.084</v>
       </c>
       <c r="Q14" t="n">
-        <v>13.383</v>
+        <v>2.395</v>
       </c>
       <c r="R14" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>6.898</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>0.598</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>0.488</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1397,52 +1397,52 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>0.08699999999999999</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0.303</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>0.726</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>5.061</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>7.255000000000001</v>
+        <v>4.943000000000001</v>
       </c>
       <c r="M15" t="n">
-        <v>9.927</v>
+        <v>14.902</v>
       </c>
       <c r="N15" t="n">
-        <v>11.825</v>
+        <v>16.19</v>
       </c>
       <c r="O15" t="n">
-        <v>10.905</v>
+        <v>29.609</v>
       </c>
       <c r="P15" t="n">
-        <v>12.72</v>
+        <v>18.365</v>
       </c>
       <c r="Q15" t="n">
-        <v>15.138</v>
+        <v>13.579</v>
       </c>
       <c r="R15" t="n">
-        <v>7.697</v>
+        <v>2.412</v>
       </c>
       <c r="S15" t="n">
-        <v>9.852</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>1.433</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>2.271</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1462,52 +1462,52 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0.075</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>0.27</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>0.8059999999999999</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>1.656</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>3.336</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>4.891999999999999</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>7.681</v>
+        <v>14.863</v>
       </c>
       <c r="N16" t="n">
-        <v>11.021</v>
+        <v>14.644</v>
       </c>
       <c r="O16" t="n">
-        <v>11.649</v>
+        <v>11.038</v>
       </c>
       <c r="P16" t="n">
-        <v>13.188</v>
+        <v>14.923</v>
       </c>
       <c r="Q16" t="n">
-        <v>13.981</v>
+        <v>25.878</v>
       </c>
       <c r="R16" t="n">
-        <v>10.396</v>
+        <v>11.227</v>
       </c>
       <c r="S16" t="n">
-        <v>12.63</v>
+        <v>7.427</v>
       </c>
       <c r="T16" t="n">
-        <v>2.593</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>5.821</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1527,52 +1527,52 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0.003</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0.047</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>0.396</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>0.7779999999999999</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>1.869</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>3.330000000000001</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>5.419</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>8.35</v>
+        <v>4.934</v>
       </c>
       <c r="O17" t="n">
-        <v>12.14</v>
+        <v>14.829</v>
       </c>
       <c r="P17" t="n">
-        <v>12.731</v>
+        <v>15.97</v>
       </c>
       <c r="Q17" t="n">
-        <v>11.954</v>
+        <v>19.779</v>
       </c>
       <c r="R17" t="n">
-        <v>12.942</v>
+        <v>25.918</v>
       </c>
       <c r="S17" t="n">
-        <v>15.255</v>
+        <v>18.57</v>
       </c>
       <c r="T17" t="n">
-        <v>4.449</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>10.336</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1598,46 +1598,46 @@
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>0.108</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>0.378</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0.8179999999999999</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>1.853</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.859</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>5.936</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>11.815</v>
+        <v>4.936999999999999</v>
       </c>
       <c r="P18" t="n">
-        <v>11.65</v>
+        <v>22.248</v>
       </c>
       <c r="Q18" t="n">
-        <v>10.413</v>
+        <v>12.357</v>
       </c>
       <c r="R18" t="n">
-        <v>14.506</v>
+        <v>29.481</v>
       </c>
       <c r="S18" t="n">
-        <v>16.337</v>
+        <v>15.028</v>
       </c>
       <c r="T18" t="n">
-        <v>7.242999999999999</v>
+        <v>13.476</v>
       </c>
       <c r="U18" t="n">
-        <v>15.082</v>
+        <v>2.473</v>
       </c>
     </row>
     <row r="19">
@@ -1666,43 +1666,43 @@
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>0.006999999999999999</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>0.118</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0.392</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0.9169999999999999</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>2.389</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>3.918</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>10.849</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>9.638</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>7.913</v>
+        <v>18.572</v>
       </c>
       <c r="R19" t="n">
-        <v>15.723</v>
+        <v>11.099</v>
       </c>
       <c r="S19" t="n">
-        <v>15.376</v>
+        <v>22.227</v>
       </c>
       <c r="T19" t="n">
-        <v>11.328</v>
+        <v>33.28</v>
       </c>
       <c r="U19" t="n">
-        <v>21.432</v>
+        <v>14.822</v>
       </c>
     </row>
     <row r="20">
@@ -1734,40 +1734,40 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>0.018</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>0.106</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0.351</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1.034</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>1.923</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>9.682</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>7.029000000000001</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.444</v>
+        <v>7.44</v>
       </c>
       <c r="R20" t="n">
-        <v>16.402</v>
+        <v>14.861</v>
       </c>
       <c r="S20" t="n">
-        <v>12.547</v>
+        <v>21.909</v>
       </c>
       <c r="T20" t="n">
-        <v>19.158</v>
+        <v>25.974</v>
       </c>
       <c r="U20" t="n">
-        <v>27.306</v>
+        <v>29.816</v>
       </c>
     </row>
     <row r="21">
@@ -1799,40 +1799,40 @@
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>0.006</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>0.07100000000000001</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.366</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>0.542</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>6.866</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>3.107</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>11.334</v>
+        <v>5.002</v>
       </c>
       <c r="S21" t="n">
-        <v>6.247</v>
+        <v>14.839</v>
       </c>
       <c r="T21" t="n">
-        <v>52.954</v>
+        <v>27.27</v>
       </c>
       <c r="U21" t="n">
-        <v>17.216</v>
+        <v>52.889</v>
       </c>
     </row>
   </sheetData>

--- a/Resultados.xlsx
+++ b/Resultados.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,142 +417,142 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Posicion</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>América de Cali</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Independiente Medellín</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Deportes Tolima</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
         <is>
           <t>Atlético Nacional</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Millonarios</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Llaneros</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Once Caldas</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Santa Fe</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Águilas Doradas</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Deportivo Cali</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Cúcuta Deportivo</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Internacional de Bogotá</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Fortaleza</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>Deportivo Pereira</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>Jaguares</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>Junior</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>Alianza Valledupar</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>Boyacá Chicó</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
         <is>
           <t>Deportivo Pasto</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Junior</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Deportes Tolima</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>América de Cali</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Once Caldas</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Internacional de Bogotá</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Santa Fe</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Deportivo Cali</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Independiente Medellín</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Millonarios</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Atlético Bucaramanga</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Águilas Doradas</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>Llaneros</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>Fortaleza</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>Cúcuta Deportivo</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>Alianza Valledupar</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Jaguares</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>Boyacá Chicó</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>Deportivo Pereira</t>
-        </is>
-      </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" t="n">
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>55.97299999999999</v>
+        <v>46.643</v>
       </c>
       <c r="C2" t="n">
-        <v>33.093</v>
+        <v>3.358</v>
       </c>
       <c r="D2" t="n">
-        <v>10.934</v>
+        <v>0.637</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>48.882</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>0.016</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>0.038</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>0.302</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>0.092</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>0.029</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -573,10 +561,10 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -601,47 +589,47 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" t="n">
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>25.767</v>
+        <v>41.415</v>
       </c>
       <c r="C3" t="n">
-        <v>33.733</v>
+        <v>12.237</v>
       </c>
       <c r="D3" t="n">
-        <v>29.574</v>
+        <v>2.907</v>
       </c>
       <c r="E3" t="n">
-        <v>10.926</v>
+        <v>39.814</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>0.249</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>0.297</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>1.758</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>0.322</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>0.022</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>0.029</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>0.011</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -666,59 +654,59 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" t="n">
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>14.549</v>
+        <v>8.976000000000001</v>
       </c>
       <c r="C4" t="n">
-        <v>7.327999999999999</v>
+        <v>44.292</v>
       </c>
       <c r="D4" t="n">
-        <v>21.292</v>
+        <v>13.924</v>
       </c>
       <c r="E4" t="n">
-        <v>37.155</v>
+        <v>8.337</v>
       </c>
       <c r="F4" t="n">
-        <v>17.19</v>
+        <v>2.427</v>
       </c>
       <c r="G4" t="n">
-        <v>2.486</v>
+        <v>2.02</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>7.69</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>2.843</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>0.309</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>0.422</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>0.119</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -731,59 +719,59 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" t="n">
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>3.711</v>
+        <v>2.102</v>
       </c>
       <c r="C5" t="n">
-        <v>18.426</v>
+        <v>19.479</v>
       </c>
       <c r="D5" t="n">
-        <v>18.582</v>
+        <v>22.826</v>
       </c>
       <c r="E5" t="n">
-        <v>17.466</v>
+        <v>1.988</v>
       </c>
       <c r="F5" t="n">
-        <v>26.023</v>
+        <v>6.614000000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>13.31</v>
+        <v>5.176</v>
       </c>
       <c r="H5" t="n">
-        <v>2.482</v>
+        <v>15.121</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>16.37</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>6.856</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1.086</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.634</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>0.195</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>0.4969999999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>0.006</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>0.049</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -796,59 +784,59 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" t="n">
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>0.608</v>
       </c>
       <c r="C6" t="n">
-        <v>7.42</v>
+        <v>9.641</v>
       </c>
       <c r="D6" t="n">
-        <v>14.772</v>
+        <v>17.758</v>
       </c>
       <c r="E6" t="n">
-        <v>14.902</v>
+        <v>0.609</v>
       </c>
       <c r="F6" t="n">
-        <v>18.406</v>
+        <v>10.79</v>
       </c>
       <c r="G6" t="n">
-        <v>25.864</v>
+        <v>8.136000000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>14.899</v>
+        <v>17.452</v>
       </c>
       <c r="I6" t="n">
-        <v>3.737</v>
+        <v>17.372</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>10.162</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>2.277</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>3.429</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>0.5479999999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1.055</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>0.003</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>0.018</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>0.142</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -861,657 +849,657 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" t="n">
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>0.163</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>5.109</v>
       </c>
       <c r="D7" t="n">
-        <v>4.846</v>
+        <v>13.264</v>
       </c>
       <c r="E7" t="n">
-        <v>14.699</v>
+        <v>0.226</v>
       </c>
       <c r="F7" t="n">
-        <v>16.092</v>
+        <v>13.642</v>
       </c>
       <c r="G7" t="n">
-        <v>19.859</v>
+        <v>10.178</v>
       </c>
       <c r="H7" t="n">
-        <v>29.553</v>
+        <v>15.845</v>
       </c>
       <c r="I7" t="n">
-        <v>14.951</v>
+        <v>15.832</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>12.688</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>3.875</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>5.711</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>1.163</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1.918</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>0.003</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>0.057</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>0.323</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" t="n">
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>0.051</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>9.901999999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>4.852</v>
+        <v>0.095</v>
       </c>
       <c r="F8" t="n">
-        <v>22.289</v>
+        <v>14.95</v>
       </c>
       <c r="G8" t="n">
-        <v>19.764</v>
+        <v>11.919</v>
       </c>
       <c r="H8" t="n">
-        <v>19.485</v>
+        <v>12.949</v>
       </c>
       <c r="I8" t="n">
-        <v>22.397</v>
+        <v>12.862</v>
       </c>
       <c r="J8" t="n">
-        <v>11.213</v>
+        <v>13.894</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>6.143</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>8.053000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>2.235</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>3.182</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>0.028</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>0.138</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>0.006999999999999999</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>0.729</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" t="n">
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>0.028</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>1.613</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>7.124999999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>0.036</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>14.813</v>
       </c>
       <c r="G9" t="n">
-        <v>14.943</v>
+        <v>12.878</v>
       </c>
       <c r="H9" t="n">
-        <v>7.463</v>
+        <v>10.08</v>
       </c>
       <c r="I9" t="n">
-        <v>20.974</v>
+        <v>10.117</v>
       </c>
       <c r="J9" t="n">
-        <v>36.921</v>
+        <v>13.801</v>
       </c>
       <c r="K9" t="n">
-        <v>17.279</v>
+        <v>8.613999999999999</v>
       </c>
       <c r="L9" t="n">
-        <v>2.42</v>
+        <v>10.714</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.691</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>4.759</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>0.053</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>0.259</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>0.014</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" t="n">
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>0.011</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>0.8330000000000001</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>5.017</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>12.546</v>
       </c>
       <c r="G10" t="n">
-        <v>3.774</v>
+        <v>13.153</v>
       </c>
       <c r="H10" t="n">
-        <v>18.668</v>
+        <v>7.324</v>
       </c>
       <c r="I10" t="n">
-        <v>18.193</v>
+        <v>7.457</v>
       </c>
       <c r="J10" t="n">
-        <v>17.461</v>
+        <v>12.631</v>
       </c>
       <c r="K10" t="n">
-        <v>25.71</v>
+        <v>11.933</v>
       </c>
       <c r="L10" t="n">
-        <v>13.648</v>
+        <v>13.575</v>
       </c>
       <c r="M10" t="n">
-        <v>2.546</v>
+        <v>5.528</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>6.73</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>0.153</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>0.494</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>0.046</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2.544</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>0.011</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" t="n">
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>0.365</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>3.287</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>9.671000000000001</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>12.247</v>
       </c>
       <c r="H11" t="n">
-        <v>7.449999999999999</v>
+        <v>4.881</v>
       </c>
       <c r="I11" t="n">
-        <v>14.813</v>
+        <v>5.155</v>
       </c>
       <c r="J11" t="n">
-        <v>14.684</v>
+        <v>10.089</v>
       </c>
       <c r="K11" t="n">
-        <v>18.612</v>
+        <v>14.674</v>
       </c>
       <c r="L11" t="n">
-        <v>25.952</v>
+        <v>15.362</v>
       </c>
       <c r="M11" t="n">
-        <v>11.136</v>
+        <v>8.189</v>
       </c>
       <c r="N11" t="n">
-        <v>7.353</v>
+        <v>9.921000000000001</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>0.369</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.059</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>4.557</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>0.038</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>0.011</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" t="n">
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>1.898</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>6.861000000000001</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>10.077</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>2.995</v>
       </c>
       <c r="I12" t="n">
-        <v>4.935</v>
+        <v>3.211</v>
       </c>
       <c r="J12" t="n">
-        <v>14.951</v>
+        <v>7.496</v>
       </c>
       <c r="K12" t="n">
-        <v>8.556999999999999</v>
+        <v>15.59</v>
       </c>
       <c r="L12" t="n">
-        <v>22.322</v>
+        <v>15.369</v>
       </c>
       <c r="M12" t="n">
-        <v>25.651</v>
+        <v>11.781</v>
       </c>
       <c r="N12" t="n">
-        <v>21.086</v>
+        <v>13.596</v>
       </c>
       <c r="O12" t="n">
-        <v>2.498</v>
+        <v>0.914</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.149</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>0.339</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>7.403</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>0.006</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>0.073</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" t="n">
         <v>12</v>
       </c>
       <c r="B13" t="n">
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>0.052</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>0.89</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>4.065</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>7.111000000000001</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>1.687</v>
       </c>
       <c r="J13" t="n">
-        <v>4.77</v>
+        <v>4.762</v>
       </c>
       <c r="K13" t="n">
-        <v>14.879</v>
+        <v>14.279</v>
       </c>
       <c r="L13" t="n">
-        <v>15.957</v>
+        <v>12.076</v>
       </c>
       <c r="M13" t="n">
-        <v>27.191</v>
+        <v>15.947</v>
       </c>
       <c r="N13" t="n">
-        <v>18.602</v>
+        <v>17.641</v>
       </c>
       <c r="O13" t="n">
-        <v>11.191</v>
+        <v>2.225</v>
       </c>
       <c r="P13" t="n">
-        <v>7.41</v>
+        <v>4.37</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>0.855</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>11.843</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>0.021</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>0.281</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>0.255</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" t="n">
         <v>13</v>
       </c>
       <c r="B14" t="n">
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>0.017</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>0.402</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>2.141</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>4.18</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>2.748</v>
       </c>
       <c r="K14" t="n">
-        <v>14.963</v>
+        <v>10.688</v>
       </c>
       <c r="L14" t="n">
-        <v>14.758</v>
+        <v>7.707999999999999</v>
       </c>
       <c r="M14" t="n">
-        <v>3.711</v>
+        <v>19.152</v>
       </c>
       <c r="N14" t="n">
-        <v>17.191</v>
+        <v>16.968</v>
       </c>
       <c r="O14" t="n">
-        <v>25.898</v>
+        <v>5.067</v>
       </c>
       <c r="P14" t="n">
-        <v>21.084</v>
+        <v>8.471</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.395</v>
+        <v>2.332</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>16.908</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>0.779</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>0.8420000000000001</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" t="n">
         <v>14</v>
       </c>
       <c r="B15" t="n">
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>0.003</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>0.126</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>0.889</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>1.878</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>0.273</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>0.313</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1.174</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>6.539000000000001</v>
       </c>
       <c r="L15" t="n">
-        <v>4.943000000000001</v>
+        <v>3.86</v>
       </c>
       <c r="M15" t="n">
-        <v>14.902</v>
+        <v>16.202</v>
       </c>
       <c r="N15" t="n">
-        <v>16.19</v>
+        <v>12.274</v>
       </c>
       <c r="O15" t="n">
-        <v>29.609</v>
+        <v>11.02</v>
       </c>
       <c r="P15" t="n">
-        <v>18.365</v>
+        <v>14.686</v>
       </c>
       <c r="Q15" t="n">
-        <v>13.579</v>
+        <v>5.846</v>
       </c>
       <c r="R15" t="n">
-        <v>2.412</v>
+        <v>20.272</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>0.281</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>1.812</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>2.552</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" t="n">
         <v>15</v>
       </c>
       <c r="B16" t="n">
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>0.034</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>0.5369999999999999</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>0.075</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>0.078</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>0.374</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>2.665</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.481</v>
       </c>
       <c r="M16" t="n">
-        <v>14.863</v>
+        <v>8.914</v>
       </c>
       <c r="N16" t="n">
-        <v>14.644</v>
+        <v>6.48</v>
       </c>
       <c r="O16" t="n">
-        <v>11.038</v>
+        <v>18.247</v>
       </c>
       <c r="P16" t="n">
-        <v>14.923</v>
+        <v>21.358</v>
       </c>
       <c r="Q16" t="n">
-        <v>25.878</v>
+        <v>12.91</v>
       </c>
       <c r="R16" t="n">
-        <v>11.227</v>
+        <v>15.05</v>
       </c>
       <c r="S16" t="n">
-        <v>7.427</v>
+        <v>0.947</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>4.182</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>6.417000000000001</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" t="n">
         <v>16</v>
       </c>
       <c r="B17" t="n">
@@ -1521,62 +1509,62 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>0.064</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>0.128</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>0.014</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>0.016</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>0.106</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>0.9730000000000001</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>0.429</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>4.144</v>
       </c>
       <c r="N17" t="n">
-        <v>4.934</v>
+        <v>2.976</v>
       </c>
       <c r="O17" t="n">
-        <v>14.829</v>
+        <v>20.9</v>
       </c>
       <c r="P17" t="n">
-        <v>15.97</v>
+        <v>19.19</v>
       </c>
       <c r="Q17" t="n">
-        <v>19.779</v>
+        <v>19.294</v>
       </c>
       <c r="R17" t="n">
-        <v>25.918</v>
+        <v>9.657999999999999</v>
       </c>
       <c r="S17" t="n">
-        <v>18.57</v>
+        <v>2.341</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>7.736</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>12.029</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" t="n">
         <v>17</v>
       </c>
       <c r="B18" t="n">
@@ -1586,62 +1574,62 @@
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>0.042</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>0.003</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>0.021</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>0.26</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>0.121</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>1.567</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>1.231</v>
       </c>
       <c r="O18" t="n">
-        <v>4.936999999999999</v>
+        <v>17.705</v>
       </c>
       <c r="P18" t="n">
-        <v>22.248</v>
+        <v>13.906</v>
       </c>
       <c r="Q18" t="n">
-        <v>12.357</v>
+        <v>23.302</v>
       </c>
       <c r="R18" t="n">
-        <v>29.481</v>
+        <v>5.233000000000001</v>
       </c>
       <c r="S18" t="n">
-        <v>15.028</v>
+        <v>5.327</v>
       </c>
       <c r="T18" t="n">
-        <v>13.476</v>
+        <v>12.551</v>
       </c>
       <c r="U18" t="n">
-        <v>2.473</v>
+        <v>18.719</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" t="n">
         <v>18</v>
       </c>
       <c r="B19" t="n">
@@ -1657,10 +1645,10 @@
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -1669,44 +1657,44 @@
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>0.004</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>0.065</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>0.022</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>0.5499999999999999</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>0.479</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>13.485</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>8.691000000000001</v>
       </c>
       <c r="Q19" t="n">
-        <v>18.572</v>
+        <v>19.723</v>
       </c>
       <c r="R19" t="n">
-        <v>11.099</v>
+        <v>2.545</v>
       </c>
       <c r="S19" t="n">
-        <v>22.227</v>
+        <v>10.866</v>
       </c>
       <c r="T19" t="n">
-        <v>33.28</v>
+        <v>18.96</v>
       </c>
       <c r="U19" t="n">
-        <v>14.822</v>
+        <v>24.603</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" t="n">
         <v>19</v>
       </c>
       <c r="B20" t="n">
@@ -1737,41 +1725,41 @@
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>0.008</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>0.136</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>7.657</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>4.145</v>
       </c>
       <c r="Q20" t="n">
-        <v>7.44</v>
+        <v>11.487</v>
       </c>
       <c r="R20" t="n">
-        <v>14.861</v>
+        <v>1.059</v>
       </c>
       <c r="S20" t="n">
-        <v>21.909</v>
+        <v>24.413</v>
       </c>
       <c r="T20" t="n">
-        <v>25.974</v>
+        <v>27.617</v>
       </c>
       <c r="U20" t="n">
-        <v>29.816</v>
+        <v>23.323</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" t="n">
         <v>20</v>
       </c>
       <c r="B21" t="n">
@@ -1808,31 +1796,31 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>0.012</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>0.025</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>1.002</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3.723</v>
       </c>
       <c r="R21" t="n">
-        <v>5.002</v>
+        <v>0.275</v>
       </c>
       <c r="S21" t="n">
-        <v>14.839</v>
+        <v>55.696</v>
       </c>
       <c r="T21" t="n">
-        <v>27.27</v>
+        <v>25.925</v>
       </c>
       <c r="U21" t="n">
-        <v>52.889</v>
+        <v>11.172</v>
       </c>
     </row>
   </sheetData>

--- a/Resultados.xlsx
+++ b/Resultados.xlsx
@@ -454,34 +454,34 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
+          <t>Santa Fe</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Águilas Doradas</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>Atlético Bucaramanga</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Once Caldas</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Santa Fe</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>Águilas Doradas</t>
-        </is>
-      </c>
       <c r="L1" t="inlineStr">
         <is>
+          <t>Cúcuta Deportivo</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
           <t>Deportivo Cali</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>Cúcuta Deportivo</t>
-        </is>
-      </c>
       <c r="N1" t="inlineStr">
         <is>
           <t>Internacional de Bogotá</t>
@@ -504,22 +504,22 @@
       </c>
       <c r="R1" t="inlineStr">
         <is>
+          <t>Boyacá Chicó</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
           <t>Junior</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>Deportivo Pasto</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
         <is>
           <t>Alianza Valledupar</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>Boyacá Chicó</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>Deportivo Pasto</t>
         </is>
       </c>
     </row>
@@ -528,43 +528,43 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>46.643</v>
+        <v>46.471</v>
       </c>
       <c r="C2" t="n">
-        <v>3.358</v>
+        <v>9.420999999999999</v>
       </c>
       <c r="D2" t="n">
-        <v>0.637</v>
+        <v>5.207</v>
       </c>
       <c r="E2" t="n">
-        <v>48.882</v>
+        <v>36.148</v>
       </c>
       <c r="F2" t="n">
-        <v>0.016</v>
+        <v>0.236</v>
       </c>
       <c r="G2" t="n">
-        <v>0.038</v>
+        <v>0.134</v>
       </c>
       <c r="H2" t="n">
-        <v>0.302</v>
+        <v>0.398</v>
       </c>
       <c r="I2" t="n">
-        <v>0.092</v>
+        <v>0.138</v>
       </c>
       <c r="J2" t="n">
-        <v>0.029</v>
+        <v>1.557</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>0.228</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>0.006999999999999999</v>
       </c>
       <c r="M2" t="n">
-        <v>0.001</v>
+        <v>0.043</v>
       </c>
       <c r="N2" t="n">
-        <v>0.002</v>
+        <v>0.005</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -579,7 +579,7 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>0.006999999999999999</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
@@ -593,58 +593,58 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>41.415</v>
+        <v>30.893</v>
       </c>
       <c r="C3" t="n">
-        <v>12.237</v>
+        <v>16.364</v>
       </c>
       <c r="D3" t="n">
-        <v>2.907</v>
+        <v>10.76</v>
       </c>
       <c r="E3" t="n">
-        <v>39.814</v>
+        <v>31.77</v>
       </c>
       <c r="F3" t="n">
-        <v>0.249</v>
+        <v>1.232</v>
       </c>
       <c r="G3" t="n">
-        <v>0.297</v>
+        <v>0.496</v>
       </c>
       <c r="H3" t="n">
-        <v>1.758</v>
+        <v>1.803</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.659</v>
       </c>
       <c r="J3" t="n">
-        <v>0.322</v>
+        <v>4.333</v>
       </c>
       <c r="K3" t="n">
-        <v>0.022</v>
+        <v>1.273</v>
       </c>
       <c r="L3" t="n">
-        <v>0.029</v>
+        <v>0.044</v>
       </c>
       <c r="M3" t="n">
+        <v>0.227</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.067</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="P3" t="n">
         <v>0.001</v>
       </c>
-      <c r="N3" t="n">
-        <v>0.011</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>0.004</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>0.003</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>0.067</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
@@ -658,58 +658,58 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>8.976000000000001</v>
+        <v>13.198</v>
       </c>
       <c r="C4" t="n">
-        <v>44.292</v>
+        <v>24.441</v>
       </c>
       <c r="D4" t="n">
-        <v>13.924</v>
+        <v>18.506</v>
       </c>
       <c r="E4" t="n">
-        <v>8.337</v>
+        <v>15.809</v>
       </c>
       <c r="F4" t="n">
-        <v>2.427</v>
+        <v>3.831</v>
       </c>
       <c r="G4" t="n">
-        <v>2.02</v>
+        <v>1.704</v>
       </c>
       <c r="H4" t="n">
-        <v>8.6</v>
+        <v>5.128</v>
       </c>
       <c r="I4" t="n">
-        <v>7.69</v>
+        <v>2.005</v>
       </c>
       <c r="J4" t="n">
-        <v>2.843</v>
+        <v>9.423</v>
       </c>
       <c r="K4" t="n">
-        <v>0.309</v>
+        <v>3.993</v>
       </c>
       <c r="L4" t="n">
-        <v>0.422</v>
+        <v>0.188</v>
       </c>
       <c r="M4" t="n">
-        <v>0.03</v>
+        <v>0.988</v>
       </c>
       <c r="N4" t="n">
-        <v>0.119</v>
+        <v>0.341</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="P4" t="n">
-        <v>0.001</v>
+        <v>0.016</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>0.021</v>
       </c>
       <c r="R4" t="n">
-        <v>0.01</v>
+        <v>0.015</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>0.373</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -723,61 +723,61 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>2.102</v>
+        <v>5.593</v>
       </c>
       <c r="C5" t="n">
-        <v>19.479</v>
+        <v>18.071</v>
       </c>
       <c r="D5" t="n">
-        <v>22.826</v>
+        <v>19.587</v>
       </c>
       <c r="E5" t="n">
-        <v>1.988</v>
+        <v>8.061999999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>6.614000000000001</v>
+        <v>7.124</v>
       </c>
       <c r="G5" t="n">
-        <v>5.176</v>
+        <v>3.568000000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>15.121</v>
+        <v>8.693</v>
       </c>
       <c r="I5" t="n">
-        <v>16.37</v>
+        <v>3.895</v>
       </c>
       <c r="J5" t="n">
-        <v>6.856</v>
+        <v>13.141</v>
       </c>
       <c r="K5" t="n">
-        <v>1.086</v>
+        <v>7.252</v>
       </c>
       <c r="L5" t="n">
-        <v>1.634</v>
+        <v>0.63</v>
       </c>
       <c r="M5" t="n">
-        <v>0.195</v>
+        <v>2.207</v>
       </c>
       <c r="N5" t="n">
-        <v>0.4969999999999999</v>
+        <v>0.9730000000000001</v>
       </c>
       <c r="O5" t="n">
-        <v>0.001</v>
+        <v>0.101</v>
       </c>
       <c r="P5" t="n">
-        <v>0.006</v>
+        <v>0.061</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>0.064</v>
       </c>
       <c r="R5" t="n">
-        <v>0.049</v>
+        <v>0.052</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>0.924</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
@@ -788,64 +788,64 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.608</v>
+        <v>2.327</v>
       </c>
       <c r="C6" t="n">
-        <v>9.641</v>
+        <v>11.566</v>
       </c>
       <c r="D6" t="n">
-        <v>17.758</v>
+        <v>14.255</v>
       </c>
       <c r="E6" t="n">
-        <v>0.609</v>
+        <v>3.973</v>
       </c>
       <c r="F6" t="n">
-        <v>10.79</v>
+        <v>10.623</v>
       </c>
       <c r="G6" t="n">
-        <v>8.136000000000001</v>
+        <v>5.596</v>
       </c>
       <c r="H6" t="n">
-        <v>17.452</v>
+        <v>11.433</v>
       </c>
       <c r="I6" t="n">
-        <v>17.372</v>
+        <v>5.888999999999999</v>
       </c>
       <c r="J6" t="n">
-        <v>10.162</v>
+        <v>14.548</v>
       </c>
       <c r="K6" t="n">
-        <v>2.277</v>
+        <v>9.904999999999999</v>
       </c>
       <c r="L6" t="n">
-        <v>3.429</v>
+        <v>1.386</v>
       </c>
       <c r="M6" t="n">
-        <v>0.5479999999999999</v>
+        <v>3.883</v>
       </c>
       <c r="N6" t="n">
-        <v>1.055</v>
+        <v>1.97</v>
       </c>
       <c r="O6" t="n">
-        <v>0.003</v>
+        <v>0.211</v>
       </c>
       <c r="P6" t="n">
-        <v>0.018</v>
+        <v>0.187</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>0.195</v>
       </c>
       <c r="R6" t="n">
-        <v>0.142</v>
+        <v>0.141</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="7">
@@ -853,64 +853,64 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>0.163</v>
+        <v>0.8959999999999999</v>
       </c>
       <c r="C7" t="n">
-        <v>5.109</v>
+        <v>7.512</v>
       </c>
       <c r="D7" t="n">
-        <v>13.264</v>
+        <v>9.933</v>
       </c>
       <c r="E7" t="n">
-        <v>0.226</v>
+        <v>1.911</v>
       </c>
       <c r="F7" t="n">
-        <v>13.642</v>
+        <v>12.499</v>
       </c>
       <c r="G7" t="n">
-        <v>10.178</v>
+        <v>7.709000000000001</v>
       </c>
       <c r="H7" t="n">
-        <v>15.845</v>
+        <v>12.148</v>
       </c>
       <c r="I7" t="n">
-        <v>15.832</v>
+        <v>7.628</v>
       </c>
       <c r="J7" t="n">
-        <v>12.688</v>
+        <v>12.848</v>
       </c>
       <c r="K7" t="n">
-        <v>3.875</v>
+        <v>11.359</v>
       </c>
       <c r="L7" t="n">
-        <v>5.711</v>
+        <v>2.549</v>
       </c>
       <c r="M7" t="n">
-        <v>1.163</v>
+        <v>5.479</v>
       </c>
       <c r="N7" t="n">
-        <v>1.918</v>
+        <v>3.03</v>
       </c>
       <c r="O7" t="n">
-        <v>0.003</v>
+        <v>0.4420000000000001</v>
       </c>
       <c r="P7" t="n">
-        <v>0.057</v>
+        <v>0.381</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.002</v>
+        <v>0.36</v>
       </c>
       <c r="R7" t="n">
-        <v>0.323</v>
+        <v>0.305</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.998</v>
       </c>
       <c r="T7" t="n">
-        <v>0.001</v>
+        <v>0.005</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="8">
@@ -918,64 +918,64 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>0.051</v>
+        <v>0.354</v>
       </c>
       <c r="C8" t="n">
-        <v>2.86</v>
+        <v>4.772</v>
       </c>
       <c r="D8" t="n">
-        <v>9.901999999999999</v>
+        <v>7.114</v>
       </c>
       <c r="E8" t="n">
-        <v>0.095</v>
+        <v>1.089</v>
       </c>
       <c r="F8" t="n">
-        <v>14.95</v>
+        <v>12.622</v>
       </c>
       <c r="G8" t="n">
-        <v>11.919</v>
+        <v>8.708</v>
       </c>
       <c r="H8" t="n">
-        <v>12.949</v>
+        <v>12.071</v>
       </c>
       <c r="I8" t="n">
-        <v>12.862</v>
+        <v>9.135999999999999</v>
       </c>
       <c r="J8" t="n">
-        <v>13.894</v>
+        <v>10.593</v>
       </c>
       <c r="K8" t="n">
-        <v>6.143</v>
+        <v>11.644</v>
       </c>
       <c r="L8" t="n">
-        <v>8.053000000000001</v>
+        <v>3.721</v>
       </c>
       <c r="M8" t="n">
-        <v>2.235</v>
+        <v>6.868</v>
       </c>
       <c r="N8" t="n">
-        <v>3.182</v>
+        <v>4.372</v>
       </c>
       <c r="O8" t="n">
-        <v>0.028</v>
+        <v>0.878</v>
       </c>
       <c r="P8" t="n">
-        <v>0.138</v>
+        <v>0.637</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.006999999999999999</v>
+        <v>0.732</v>
       </c>
       <c r="R8" t="n">
-        <v>0.729</v>
+        <v>0.5459999999999999</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>4.085</v>
       </c>
       <c r="T8" t="n">
-        <v>0.002</v>
+        <v>0.019</v>
       </c>
       <c r="U8" t="n">
-        <v>0.001</v>
+        <v>0.039</v>
       </c>
     </row>
     <row r="9">
@@ -983,64 +983,64 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>0.028</v>
+        <v>0.18</v>
       </c>
       <c r="C9" t="n">
-        <v>1.613</v>
+        <v>3.064</v>
       </c>
       <c r="D9" t="n">
-        <v>7.124999999999999</v>
+        <v>4.973000000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>0.036</v>
+        <v>0.5950000000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>14.813</v>
+        <v>11.845</v>
       </c>
       <c r="G9" t="n">
-        <v>12.878</v>
+        <v>9.75</v>
       </c>
       <c r="H9" t="n">
-        <v>10.08</v>
+        <v>10.888</v>
       </c>
       <c r="I9" t="n">
-        <v>10.117</v>
+        <v>10.02</v>
       </c>
       <c r="J9" t="n">
-        <v>13.801</v>
+        <v>8.76</v>
       </c>
       <c r="K9" t="n">
-        <v>8.613999999999999</v>
+        <v>11.267</v>
       </c>
       <c r="L9" t="n">
-        <v>10.714</v>
+        <v>5.069</v>
       </c>
       <c r="M9" t="n">
-        <v>3.691</v>
+        <v>8.092000000000001</v>
       </c>
       <c r="N9" t="n">
-        <v>4.759</v>
+        <v>5.664000000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>0.053</v>
+        <v>1.395</v>
       </c>
       <c r="P9" t="n">
-        <v>0.259</v>
+        <v>1.002</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.014</v>
+        <v>1.142</v>
       </c>
       <c r="R9" t="n">
-        <v>1.4</v>
+        <v>0.8160000000000001</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>5.361</v>
       </c>
       <c r="T9" t="n">
-        <v>0.005</v>
+        <v>0.045</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>0.07200000000000001</v>
       </c>
     </row>
     <row r="10">
@@ -1048,64 +1048,64 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>0.011</v>
+        <v>0.043</v>
       </c>
       <c r="C10" t="n">
-        <v>0.8330000000000001</v>
+        <v>2.018</v>
       </c>
       <c r="D10" t="n">
-        <v>5.017</v>
+        <v>3.565</v>
       </c>
       <c r="E10" t="n">
-        <v>0.01</v>
+        <v>0.332</v>
       </c>
       <c r="F10" t="n">
-        <v>12.546</v>
+        <v>10.455</v>
       </c>
       <c r="G10" t="n">
-        <v>13.153</v>
+        <v>10.175</v>
       </c>
       <c r="H10" t="n">
-        <v>7.324</v>
+        <v>9.281000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>7.457</v>
+        <v>10.338</v>
       </c>
       <c r="J10" t="n">
-        <v>12.631</v>
+        <v>7.045999999999999</v>
       </c>
       <c r="K10" t="n">
-        <v>11.933</v>
+        <v>10.102</v>
       </c>
       <c r="L10" t="n">
-        <v>13.575</v>
+        <v>6.5</v>
       </c>
       <c r="M10" t="n">
-        <v>5.528</v>
+        <v>9.191000000000001</v>
       </c>
       <c r="N10" t="n">
-        <v>6.73</v>
+        <v>7.193</v>
       </c>
       <c r="O10" t="n">
-        <v>0.153</v>
+        <v>2.218</v>
       </c>
       <c r="P10" t="n">
-        <v>0.494</v>
+        <v>1.676</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.046</v>
+        <v>1.714</v>
       </c>
       <c r="R10" t="n">
-        <v>2.544</v>
+        <v>1.334</v>
       </c>
       <c r="S10" t="n">
-        <v>0.001</v>
+        <v>6.557</v>
       </c>
       <c r="T10" t="n">
-        <v>0.011</v>
+        <v>0.107</v>
       </c>
       <c r="U10" t="n">
-        <v>0.003</v>
+        <v>0.155</v>
       </c>
     </row>
     <row r="11">
@@ -1113,64 +1113,64 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>0.002</v>
+        <v>0.032</v>
       </c>
       <c r="C11" t="n">
-        <v>0.365</v>
+        <v>1.213</v>
       </c>
       <c r="D11" t="n">
-        <v>3.287</v>
+        <v>2.408</v>
       </c>
       <c r="E11" t="n">
-        <v>0.002</v>
+        <v>0.159</v>
       </c>
       <c r="F11" t="n">
-        <v>9.671000000000001</v>
+        <v>8.712999999999999</v>
       </c>
       <c r="G11" t="n">
-        <v>12.247</v>
+        <v>10.301</v>
       </c>
       <c r="H11" t="n">
-        <v>4.881</v>
+        <v>7.928</v>
       </c>
       <c r="I11" t="n">
-        <v>5.155</v>
+        <v>10.231</v>
       </c>
       <c r="J11" t="n">
-        <v>10.089</v>
+        <v>5.4</v>
       </c>
       <c r="K11" t="n">
-        <v>14.674</v>
+        <v>8.785</v>
       </c>
       <c r="L11" t="n">
-        <v>15.362</v>
+        <v>8.007999999999999</v>
       </c>
       <c r="M11" t="n">
-        <v>8.189</v>
+        <v>9.812999999999999</v>
       </c>
       <c r="N11" t="n">
-        <v>9.921000000000001</v>
+        <v>8.523999999999999</v>
       </c>
       <c r="O11" t="n">
-        <v>0.369</v>
+        <v>3.129</v>
       </c>
       <c r="P11" t="n">
-        <v>1.059</v>
+        <v>2.404</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.12</v>
+        <v>2.561</v>
       </c>
       <c r="R11" t="n">
-        <v>4.557</v>
+        <v>2.075</v>
       </c>
       <c r="S11" t="n">
-        <v>0.001</v>
+        <v>7.846</v>
       </c>
       <c r="T11" t="n">
-        <v>0.038</v>
+        <v>0.209</v>
       </c>
       <c r="U11" t="n">
-        <v>0.011</v>
+        <v>0.261</v>
       </c>
     </row>
     <row r="12">
@@ -1178,64 +1178,64 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>0.001</v>
+        <v>0.012</v>
       </c>
       <c r="C12" t="n">
-        <v>0.14</v>
+        <v>0.737</v>
       </c>
       <c r="D12" t="n">
-        <v>1.898</v>
+        <v>1.58</v>
       </c>
       <c r="E12" t="n">
-        <v>0.001</v>
+        <v>0.075</v>
       </c>
       <c r="F12" t="n">
-        <v>6.861000000000001</v>
+        <v>6.717</v>
       </c>
       <c r="G12" t="n">
-        <v>10.077</v>
+        <v>9.635999999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>2.995</v>
+        <v>6.250999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>3.211</v>
+        <v>9.699</v>
       </c>
       <c r="J12" t="n">
-        <v>7.496</v>
+        <v>4.188</v>
       </c>
       <c r="K12" t="n">
-        <v>15.59</v>
+        <v>7.313</v>
       </c>
       <c r="L12" t="n">
-        <v>15.369</v>
+        <v>9.336</v>
       </c>
       <c r="M12" t="n">
-        <v>11.781</v>
+        <v>10.216</v>
       </c>
       <c r="N12" t="n">
-        <v>13.596</v>
+        <v>9.775</v>
       </c>
       <c r="O12" t="n">
-        <v>0.914</v>
+        <v>4.499000000000001</v>
       </c>
       <c r="P12" t="n">
-        <v>2.149</v>
+        <v>3.617</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.339</v>
+        <v>3.763</v>
       </c>
       <c r="R12" t="n">
-        <v>7.403</v>
+        <v>2.985</v>
       </c>
       <c r="S12" t="n">
-        <v>0.006</v>
+        <v>8.824999999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1</v>
+        <v>0.354</v>
       </c>
       <c r="U12" t="n">
-        <v>0.073</v>
+        <v>0.422</v>
       </c>
     </row>
     <row r="13">
@@ -1243,64 +1243,64 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="C13" t="n">
-        <v>0.052</v>
+        <v>0.426</v>
       </c>
       <c r="D13" t="n">
-        <v>0.89</v>
+        <v>1.008</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>0.039</v>
       </c>
       <c r="F13" t="n">
-        <v>4.065</v>
+        <v>5.251</v>
       </c>
       <c r="G13" t="n">
-        <v>7.111000000000001</v>
+        <v>8.781000000000001</v>
       </c>
       <c r="H13" t="n">
-        <v>1.64</v>
+        <v>4.766</v>
       </c>
       <c r="I13" t="n">
-        <v>1.687</v>
+        <v>8.343999999999999</v>
       </c>
       <c r="J13" t="n">
-        <v>4.762</v>
+        <v>2.937</v>
       </c>
       <c r="K13" t="n">
-        <v>14.279</v>
+        <v>5.697</v>
       </c>
       <c r="L13" t="n">
-        <v>12.076</v>
+        <v>10.591</v>
       </c>
       <c r="M13" t="n">
-        <v>15.947</v>
+        <v>9.835000000000001</v>
       </c>
       <c r="N13" t="n">
-        <v>17.641</v>
+        <v>10.723</v>
       </c>
       <c r="O13" t="n">
-        <v>2.225</v>
+        <v>6.154</v>
       </c>
       <c r="P13" t="n">
-        <v>4.37</v>
+        <v>4.966</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.855</v>
+        <v>5.262</v>
       </c>
       <c r="R13" t="n">
-        <v>11.843</v>
+        <v>4.156</v>
       </c>
       <c r="S13" t="n">
-        <v>0.021</v>
+        <v>9.496</v>
       </c>
       <c r="T13" t="n">
-        <v>0.281</v>
+        <v>0.7779999999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>0.255</v>
+        <v>0.7889999999999999</v>
       </c>
     </row>
     <row r="14">
@@ -1311,61 +1311,61 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>0.017</v>
+        <v>0.223</v>
       </c>
       <c r="D14" t="n">
-        <v>0.402</v>
+        <v>0.5329999999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>0.023</v>
       </c>
       <c r="F14" t="n">
-        <v>2.141</v>
+        <v>3.654</v>
       </c>
       <c r="G14" t="n">
-        <v>4.18</v>
+        <v>7.3</v>
       </c>
       <c r="H14" t="n">
-        <v>0.6899999999999999</v>
+        <v>3.59</v>
       </c>
       <c r="I14" t="n">
-        <v>0.8070000000000001</v>
+        <v>7.074</v>
       </c>
       <c r="J14" t="n">
-        <v>2.748</v>
+        <v>2.158</v>
       </c>
       <c r="K14" t="n">
-        <v>10.688</v>
+        <v>4.344</v>
       </c>
       <c r="L14" t="n">
-        <v>7.707999999999999</v>
+        <v>11.227</v>
       </c>
       <c r="M14" t="n">
-        <v>19.152</v>
+        <v>9.023</v>
       </c>
       <c r="N14" t="n">
-        <v>16.968</v>
+        <v>10.871</v>
       </c>
       <c r="O14" t="n">
-        <v>5.067</v>
+        <v>8.109</v>
       </c>
       <c r="P14" t="n">
-        <v>8.471</v>
+        <v>6.741</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.332</v>
+        <v>6.973999999999999</v>
       </c>
       <c r="R14" t="n">
-        <v>16.908</v>
+        <v>5.633</v>
       </c>
       <c r="S14" t="n">
-        <v>0.1</v>
+        <v>9.932</v>
       </c>
       <c r="T14" t="n">
-        <v>0.779</v>
+        <v>1.295</v>
       </c>
       <c r="U14" t="n">
-        <v>0.8420000000000001</v>
+        <v>1.296</v>
       </c>
     </row>
     <row r="15">
@@ -1376,61 +1376,61 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>0.003</v>
+        <v>0.107</v>
       </c>
       <c r="D15" t="n">
-        <v>0.126</v>
+        <v>0.32</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>0.011</v>
       </c>
       <c r="F15" t="n">
-        <v>0.889</v>
+        <v>2.412</v>
       </c>
       <c r="G15" t="n">
-        <v>1.878</v>
+        <v>5.975</v>
       </c>
       <c r="H15" t="n">
-        <v>0.273</v>
+        <v>2.473</v>
       </c>
       <c r="I15" t="n">
-        <v>0.313</v>
+        <v>5.538</v>
       </c>
       <c r="J15" t="n">
-        <v>1.174</v>
+        <v>1.354</v>
       </c>
       <c r="K15" t="n">
-        <v>6.539000000000001</v>
+        <v>2.941</v>
       </c>
       <c r="L15" t="n">
-        <v>3.86</v>
+        <v>11.034</v>
       </c>
       <c r="M15" t="n">
-        <v>16.202</v>
+        <v>7.778</v>
       </c>
       <c r="N15" t="n">
-        <v>12.274</v>
+        <v>10.076</v>
       </c>
       <c r="O15" t="n">
-        <v>11.02</v>
+        <v>10.097</v>
       </c>
       <c r="P15" t="n">
-        <v>14.686</v>
+        <v>8.878</v>
       </c>
       <c r="Q15" t="n">
-        <v>5.846</v>
+        <v>9.212</v>
       </c>
       <c r="R15" t="n">
-        <v>20.272</v>
+        <v>7.455</v>
       </c>
       <c r="S15" t="n">
-        <v>0.281</v>
+        <v>9.907999999999999</v>
       </c>
       <c r="T15" t="n">
-        <v>1.812</v>
+        <v>2.358</v>
       </c>
       <c r="U15" t="n">
-        <v>2.552</v>
+        <v>2.073</v>
       </c>
     </row>
     <row r="16">
@@ -1441,61 +1441,61 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0.001</v>
+        <v>0.039</v>
       </c>
       <c r="D16" t="n">
-        <v>0.034</v>
+        <v>0.145</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>0.004</v>
       </c>
       <c r="F16" t="n">
-        <v>0.25</v>
+        <v>1.456</v>
       </c>
       <c r="G16" t="n">
-        <v>0.5369999999999999</v>
+        <v>4.386</v>
       </c>
       <c r="H16" t="n">
-        <v>0.075</v>
+        <v>1.51</v>
       </c>
       <c r="I16" t="n">
-        <v>0.078</v>
+        <v>4.016</v>
       </c>
       <c r="J16" t="n">
-        <v>0.374</v>
+        <v>0.8580000000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>2.665</v>
+        <v>1.871</v>
       </c>
       <c r="L16" t="n">
-        <v>1.481</v>
+        <v>9.695</v>
       </c>
       <c r="M16" t="n">
-        <v>8.914</v>
+        <v>6.109</v>
       </c>
       <c r="N16" t="n">
-        <v>6.48</v>
+        <v>8.68</v>
       </c>
       <c r="O16" t="n">
-        <v>18.247</v>
+        <v>12.133</v>
       </c>
       <c r="P16" t="n">
-        <v>21.358</v>
+        <v>11.301</v>
       </c>
       <c r="Q16" t="n">
-        <v>12.91</v>
+        <v>11.301</v>
       </c>
       <c r="R16" t="n">
-        <v>15.05</v>
+        <v>9.772</v>
       </c>
       <c r="S16" t="n">
-        <v>0.947</v>
+        <v>9.112</v>
       </c>
       <c r="T16" t="n">
-        <v>4.182</v>
+        <v>4.118</v>
       </c>
       <c r="U16" t="n">
-        <v>6.417000000000001</v>
+        <v>3.494</v>
       </c>
     </row>
     <row r="17">
@@ -1506,61 +1506,61 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>0.016</v>
       </c>
       <c r="D17" t="n">
-        <v>0.002</v>
+        <v>0.067</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>0.064</v>
+        <v>0.765</v>
       </c>
       <c r="G17" t="n">
-        <v>0.128</v>
+        <v>2.904</v>
       </c>
       <c r="H17" t="n">
-        <v>0.014</v>
+        <v>0.89</v>
       </c>
       <c r="I17" t="n">
-        <v>0.016</v>
+        <v>2.726</v>
       </c>
       <c r="J17" t="n">
-        <v>0.106</v>
+        <v>0.479</v>
       </c>
       <c r="K17" t="n">
-        <v>0.9730000000000001</v>
+        <v>1.132</v>
       </c>
       <c r="L17" t="n">
-        <v>0.429</v>
+        <v>7.983</v>
       </c>
       <c r="M17" t="n">
-        <v>4.144</v>
+        <v>4.489</v>
       </c>
       <c r="N17" t="n">
-        <v>2.976</v>
+        <v>6.976</v>
       </c>
       <c r="O17" t="n">
-        <v>20.9</v>
+        <v>13.569</v>
       </c>
       <c r="P17" t="n">
-        <v>19.19</v>
+        <v>12.923</v>
       </c>
       <c r="Q17" t="n">
-        <v>19.294</v>
+        <v>13.102</v>
       </c>
       <c r="R17" t="n">
-        <v>9.657999999999999</v>
+        <v>12.12</v>
       </c>
       <c r="S17" t="n">
-        <v>2.341</v>
+        <v>7.76</v>
       </c>
       <c r="T17" t="n">
-        <v>7.736</v>
+        <v>6.500999999999999</v>
       </c>
       <c r="U17" t="n">
-        <v>12.029</v>
+        <v>5.598</v>
       </c>
     </row>
     <row r="18">
@@ -1571,61 +1571,61 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>0.006999999999999999</v>
       </c>
       <c r="D18" t="n">
-        <v>0.001</v>
+        <v>0.031</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>0.01</v>
+        <v>0.378</v>
       </c>
       <c r="G18" t="n">
-        <v>0.042</v>
+        <v>1.656</v>
       </c>
       <c r="H18" t="n">
-        <v>0.001</v>
+        <v>0.485</v>
       </c>
       <c r="I18" t="n">
-        <v>0.003</v>
+        <v>1.594</v>
       </c>
       <c r="J18" t="n">
-        <v>0.021</v>
+        <v>0.252</v>
       </c>
       <c r="K18" t="n">
-        <v>0.26</v>
+        <v>0.5579999999999999</v>
       </c>
       <c r="L18" t="n">
-        <v>0.121</v>
+        <v>5.895</v>
       </c>
       <c r="M18" t="n">
-        <v>1.567</v>
+        <v>3.025</v>
       </c>
       <c r="N18" t="n">
-        <v>1.231</v>
+        <v>5.186</v>
       </c>
       <c r="O18" t="n">
-        <v>17.705</v>
+        <v>13.419</v>
       </c>
       <c r="P18" t="n">
-        <v>13.906</v>
+        <v>14.325</v>
       </c>
       <c r="Q18" t="n">
-        <v>23.302</v>
+        <v>13.761</v>
       </c>
       <c r="R18" t="n">
-        <v>5.233000000000001</v>
+        <v>14.194</v>
       </c>
       <c r="S18" t="n">
-        <v>5.327</v>
+        <v>6.15</v>
       </c>
       <c r="T18" t="n">
-        <v>12.551</v>
+        <v>10.317</v>
       </c>
       <c r="U18" t="n">
-        <v>18.719</v>
+        <v>8.766999999999999</v>
       </c>
     </row>
     <row r="19">
@@ -1636,61 +1636,61 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>0.003</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>0.006</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>0.002</v>
+        <v>0.143</v>
       </c>
       <c r="G19" t="n">
-        <v>0.005</v>
+        <v>0.8130000000000001</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>0.188</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>0.748</v>
       </c>
       <c r="J19" t="n">
-        <v>0.004</v>
+        <v>0.093</v>
       </c>
       <c r="K19" t="n">
-        <v>0.065</v>
+        <v>0.252</v>
       </c>
       <c r="L19" t="n">
-        <v>0.022</v>
+        <v>3.777</v>
       </c>
       <c r="M19" t="n">
-        <v>0.5499999999999999</v>
+        <v>1.745</v>
       </c>
       <c r="N19" t="n">
-        <v>0.479</v>
+        <v>3.367</v>
       </c>
       <c r="O19" t="n">
-        <v>13.485</v>
+        <v>11.797</v>
       </c>
       <c r="P19" t="n">
-        <v>8.691000000000001</v>
+        <v>14.517</v>
       </c>
       <c r="Q19" t="n">
-        <v>19.723</v>
+        <v>13.267</v>
       </c>
       <c r="R19" t="n">
-        <v>2.545</v>
+        <v>15.094</v>
       </c>
       <c r="S19" t="n">
-        <v>10.866</v>
+        <v>4.599</v>
       </c>
       <c r="T19" t="n">
-        <v>18.96</v>
+        <v>15.81</v>
       </c>
       <c r="U19" t="n">
-        <v>24.603</v>
+        <v>13.781</v>
       </c>
     </row>
     <row r="20">
@@ -1704,58 +1704,58 @@
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>0.039</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>0.338</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>0.06899999999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>0.265</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="K20" t="n">
-        <v>0.008</v>
+        <v>0.073</v>
       </c>
       <c r="L20" t="n">
-        <v>0.005</v>
+        <v>1.852</v>
       </c>
       <c r="M20" t="n">
-        <v>0.15</v>
+        <v>0.772</v>
       </c>
       <c r="N20" t="n">
-        <v>0.136</v>
+        <v>1.68</v>
       </c>
       <c r="O20" t="n">
-        <v>7.657</v>
+        <v>8.157999999999999</v>
       </c>
       <c r="P20" t="n">
-        <v>4.145</v>
+        <v>10.992</v>
       </c>
       <c r="Q20" t="n">
-        <v>11.487</v>
+        <v>10.506</v>
       </c>
       <c r="R20" t="n">
-        <v>1.059</v>
+        <v>13.835</v>
       </c>
       <c r="S20" t="n">
-        <v>24.413</v>
+        <v>2.811</v>
       </c>
       <c r="T20" t="n">
-        <v>27.617</v>
+        <v>25.176</v>
       </c>
       <c r="U20" t="n">
-        <v>23.323</v>
+        <v>23.402</v>
       </c>
     </row>
     <row r="21">
@@ -1775,52 +1775,52 @@
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>0.006999999999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>0.057</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>0.011</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>0.508</v>
       </c>
       <c r="M21" t="n">
-        <v>0.012</v>
+        <v>0.217</v>
       </c>
       <c r="N21" t="n">
-        <v>0.025</v>
+        <v>0.527</v>
       </c>
       <c r="O21" t="n">
-        <v>2.17</v>
+        <v>3.667</v>
       </c>
       <c r="P21" t="n">
-        <v>1.002</v>
+        <v>5.375</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.723</v>
+        <v>6.059</v>
       </c>
       <c r="R21" t="n">
-        <v>0.275</v>
+        <v>9.468999999999999</v>
       </c>
       <c r="S21" t="n">
-        <v>55.696</v>
+        <v>1.279</v>
       </c>
       <c r="T21" t="n">
-        <v>25.925</v>
+        <v>32.905</v>
       </c>
       <c r="U21" t="n">
-        <v>11.172</v>
+        <v>39.842</v>
       </c>
     </row>
   </sheetData>
